--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,53 +506,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M2" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q2" t="n">
         <v>6.43</v>
@@ -561,878 +561,878 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C3" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F3" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K3" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M3" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O3" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E4" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J4" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K4" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M4" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N4" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P4" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F5" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H5" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I5" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J5" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L5" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O5" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P5" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N6" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O6" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M7" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D8" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H8" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M8" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O8" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5.6597</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H9" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K9" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C10" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M10" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N10" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G11" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M11" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M12" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O12" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C13" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O13" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K14" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M14" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N14" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E15" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F15" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J15" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K15" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M15" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6625</v>
+        <v>5.5658</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7202</v>
+        <v>5.7355</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7715</v>
+        <v>5.8092</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9151</v>
+        <v>5.931</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0499</v>
+        <v>6.017</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2097</v>
+        <v>6.1386</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6379</v>
+        <v>6.6308</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9498</v>
+        <v>6.9463</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2695</v>
+        <v>7.269</v>
       </c>
       <c r="K16" t="n">
-        <v>7.5701</v>
+        <v>7.5719</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8275</v>
+        <v>7.8308</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0183</v>
+        <v>8.022</v>
       </c>
       <c r="N16" t="n">
-        <v>8.116</v>
+        <v>8.1187</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0907</v>
+        <v>8.0906</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9118</v>
+        <v>7.9068</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6627</v>
+        <v>5.6625</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8449</v>
+        <v>5.7202</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9075</v>
+        <v>5.7715</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9751</v>
+        <v>5.9151</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0027</v>
+        <v>6.0499</v>
       </c>
       <c r="G17" t="n">
-        <v>6.0823</v>
+        <v>6.2097</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6327</v>
+        <v>6.6379</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9478</v>
+        <v>6.9498</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2701</v>
+        <v>7.2695</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5723</v>
+        <v>7.5701</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8299</v>
+        <v>7.8275</v>
       </c>
       <c r="M17" t="n">
-        <v>8.019</v>
+        <v>8.0183</v>
       </c>
       <c r="N17" t="n">
-        <v>8.112500000000001</v>
+        <v>8.116</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0801</v>
+        <v>8.0907</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8909</v>
+        <v>7.9118</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6665</v>
+        <v>5.6627</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7561</v>
+        <v>5.8449</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8011</v>
+        <v>5.9075</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8897</v>
+        <v>5.9751</v>
       </c>
       <c r="F18" t="n">
-        <v>5.9603</v>
+        <v>6.0027</v>
       </c>
       <c r="G18" t="n">
         <v>6.0823</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6259</v>
+        <v>6.6327</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9462</v>
+        <v>6.9478</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2729</v>
+        <v>7.2701</v>
       </c>
       <c r="K18" t="n">
-        <v>7.5783</v>
+        <v>7.5723</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8377</v>
+        <v>7.8299</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0267</v>
+        <v>8.019</v>
       </c>
       <c r="N18" t="n">
-        <v>8.117599999999999</v>
+        <v>8.112500000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0794</v>
+        <v>8.0801</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8808</v>
+        <v>7.8909</v>
       </c>
       <c r="Q18" t="n">
         <v>6.44</v>
@@ -1441,108 +1441,108 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7242</v>
+        <v>5.6665</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7821</v>
+        <v>5.7561</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8221</v>
+        <v>5.8011</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9218</v>
+        <v>5.8897</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0112</v>
+        <v>5.9603</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1292</v>
+        <v>6.0823</v>
       </c>
       <c r="H19" t="n">
-        <v>6.592</v>
+        <v>6.6259</v>
       </c>
       <c r="I19" t="n">
-        <v>6.926</v>
+        <v>6.9462</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2639</v>
+        <v>7.2729</v>
       </c>
       <c r="K19" t="n">
         <v>7.5783</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8443</v>
+        <v>7.8377</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0367</v>
+        <v>8.0267</v>
       </c>
       <c r="N19" t="n">
-        <v>8.126799999999999</v>
+        <v>8.117599999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.082700000000001</v>
+        <v>8.0794</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8723</v>
+        <v>7.8808</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6184</v>
+        <v>5.7242</v>
       </c>
       <c r="C20" t="n">
-        <v>5.8008</v>
+        <v>5.7821</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8761</v>
+        <v>5.8221</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9928</v>
+        <v>5.9218</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0709</v>
+        <v>6.0112</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1692</v>
+        <v>6.1292</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6173</v>
+        <v>6.592</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9488</v>
+        <v>6.926</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2847</v>
+        <v>7.2639</v>
       </c>
       <c r="K20" t="n">
-        <v>7.597</v>
+        <v>7.5783</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8598</v>
+        <v>7.8443</v>
       </c>
       <c r="M20" t="n">
-        <v>8.047499999999999</v>
+        <v>8.0367</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1309</v>
+        <v>8.126799999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0777</v>
+        <v>8.082700000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8556</v>
+        <v>7.8723</v>
       </c>
       <c r="Q20" t="n">
         <v>6.45</v>
@@ -1551,166 +1551,56 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.567</v>
+        <v>5.6184</v>
       </c>
       <c r="C21" t="n">
-        <v>5.766</v>
+        <v>5.8008</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8799</v>
+        <v>5.8761</v>
       </c>
       <c r="E21" t="n">
-        <v>6.0204</v>
+        <v>5.9928</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0914</v>
+        <v>6.0709</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1765</v>
+        <v>6.1692</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6237</v>
+        <v>6.6173</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9524</v>
+        <v>6.9488</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2861</v>
+        <v>7.2847</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5966</v>
+        <v>7.597</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8582</v>
+        <v>7.8598</v>
       </c>
       <c r="M21" t="n">
-        <v>8.045400000000001</v>
+        <v>8.047499999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1294</v>
+        <v>8.1309</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0779</v>
+        <v>8.0777</v>
       </c>
       <c r="P21" t="n">
-        <v>7.859</v>
+        <v>7.8556</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.46</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.7041</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.8343</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.8934</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.9979</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.0758</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.1775</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.6255</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6.9534</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7.2865</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.5965</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.8578</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8.045</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.129200000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.0784</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.8605</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.49</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5.8045</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.9051</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5.9505</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6.0306</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.0902</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.1768</v>
-      </c>
-      <c r="H23" t="n">
-        <v>6.6275</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6.9545</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7.2869</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.5965</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.8574</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.044499999999999</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8.129</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.078799999999999</v>
-      </c>
-      <c r="P23" t="n">
-        <v>7.862</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,108 +506,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F2" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M2" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N2" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F3" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M3" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q3" t="n">
         <v>6.43</v>
@@ -616,878 +616,878 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C4" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J4" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K4" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O4" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D5" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E5" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F5" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J5" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K5" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M5" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N5" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P5" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F6" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H6" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I6" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L6" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O6" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N7" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O7" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J8" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M8" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D9" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H9" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M9" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O9" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>5.6597</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H10" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K10" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C11" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M11" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N11" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G12" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M12" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M13" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O14" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K15" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M15" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N15" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E16" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F16" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J16" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K16" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M16" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6625</v>
+        <v>5.5658</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7202</v>
+        <v>5.7355</v>
       </c>
       <c r="D17" t="n">
-        <v>5.7715</v>
+        <v>5.8092</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9151</v>
+        <v>5.931</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0499</v>
+        <v>6.017</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2097</v>
+        <v>6.1386</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6379</v>
+        <v>6.6308</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9498</v>
+        <v>6.9463</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2695</v>
+        <v>7.269</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5701</v>
+        <v>7.5719</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8275</v>
+        <v>7.8308</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0183</v>
+        <v>8.022</v>
       </c>
       <c r="N17" t="n">
-        <v>8.116</v>
+        <v>8.1187</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0907</v>
+        <v>8.0906</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9118</v>
+        <v>7.9068</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6627</v>
+        <v>5.6625</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8449</v>
+        <v>5.7202</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9075</v>
+        <v>5.7715</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9751</v>
+        <v>5.9151</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0027</v>
+        <v>6.0499</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0823</v>
+        <v>6.2097</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6327</v>
+        <v>6.6379</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9478</v>
+        <v>6.9498</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2701</v>
+        <v>7.2695</v>
       </c>
       <c r="K18" t="n">
-        <v>7.5723</v>
+        <v>7.5701</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8299</v>
+        <v>7.8275</v>
       </c>
       <c r="M18" t="n">
-        <v>8.019</v>
+        <v>8.0183</v>
       </c>
       <c r="N18" t="n">
-        <v>8.112500000000001</v>
+        <v>8.116</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0801</v>
+        <v>8.0907</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8909</v>
+        <v>7.9118</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6665</v>
+        <v>5.6627</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7561</v>
+        <v>5.8449</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8011</v>
+        <v>5.9075</v>
       </c>
       <c r="E19" t="n">
-        <v>5.8897</v>
+        <v>5.9751</v>
       </c>
       <c r="F19" t="n">
-        <v>5.9603</v>
+        <v>6.0027</v>
       </c>
       <c r="G19" t="n">
         <v>6.0823</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6259</v>
+        <v>6.6327</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9462</v>
+        <v>6.9478</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2729</v>
+        <v>7.2701</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5783</v>
+        <v>7.5723</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8377</v>
+        <v>7.8299</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0267</v>
+        <v>8.019</v>
       </c>
       <c r="N19" t="n">
-        <v>8.117599999999999</v>
+        <v>8.112500000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0794</v>
+        <v>8.0801</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8808</v>
+        <v>7.8909</v>
       </c>
       <c r="Q19" t="n">
         <v>6.44</v>
@@ -1496,108 +1496,108 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7242</v>
+        <v>5.6665</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7821</v>
+        <v>5.7561</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8221</v>
+        <v>5.8011</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9218</v>
+        <v>5.8897</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0112</v>
+        <v>5.9603</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1292</v>
+        <v>6.0823</v>
       </c>
       <c r="H20" t="n">
-        <v>6.592</v>
+        <v>6.6259</v>
       </c>
       <c r="I20" t="n">
-        <v>6.926</v>
+        <v>6.9462</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2639</v>
+        <v>7.2729</v>
       </c>
       <c r="K20" t="n">
         <v>7.5783</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8443</v>
+        <v>7.8377</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0367</v>
+        <v>8.0267</v>
       </c>
       <c r="N20" t="n">
-        <v>8.126799999999999</v>
+        <v>8.117599999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.082700000000001</v>
+        <v>8.0794</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8723</v>
+        <v>7.8808</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6184</v>
+        <v>5.7242</v>
       </c>
       <c r="C21" t="n">
-        <v>5.8008</v>
+        <v>5.7821</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8761</v>
+        <v>5.8221</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9928</v>
+        <v>5.9218</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0709</v>
+        <v>6.0112</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1692</v>
+        <v>6.1292</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6173</v>
+        <v>6.592</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9488</v>
+        <v>6.926</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2847</v>
+        <v>7.2639</v>
       </c>
       <c r="K21" t="n">
-        <v>7.597</v>
+        <v>7.5783</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8598</v>
+        <v>7.8443</v>
       </c>
       <c r="M21" t="n">
-        <v>8.047499999999999</v>
+        <v>8.0367</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1309</v>
+        <v>8.126799999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0777</v>
+        <v>8.082700000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8556</v>
+        <v>7.8723</v>
       </c>
       <c r="Q21" t="n">
         <v>6.45</v>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,163 +506,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E2" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G2" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J2" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N2" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C3" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F3" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M3" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N3" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G4" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M4" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q4" t="n">
         <v>6.43</v>
@@ -671,878 +671,878 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C5" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F5" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J5" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K5" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O5" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D6" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E6" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K6" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M6" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N6" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F7" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H7" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I7" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L7" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O7" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J8" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N8" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O8" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J9" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M9" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D10" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H10" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M10" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O10" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>5.6597</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H11" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K11" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C12" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M12" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N12" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G13" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M13" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M14" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C15" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O15" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K16" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M16" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N16" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E17" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F17" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J17" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M17" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6625</v>
+        <v>5.5658</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7202</v>
+        <v>5.7355</v>
       </c>
       <c r="D18" t="n">
-        <v>5.7715</v>
+        <v>5.8092</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9151</v>
+        <v>5.931</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0499</v>
+        <v>6.017</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2097</v>
+        <v>6.1386</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6379</v>
+        <v>6.6308</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9498</v>
+        <v>6.9463</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2695</v>
+        <v>7.269</v>
       </c>
       <c r="K18" t="n">
-        <v>7.5701</v>
+        <v>7.5719</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8275</v>
+        <v>7.8308</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0183</v>
+        <v>8.022</v>
       </c>
       <c r="N18" t="n">
-        <v>8.116</v>
+        <v>8.1187</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0907</v>
+        <v>8.0906</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9118</v>
+        <v>7.9068</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6627</v>
+        <v>5.6625</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8449</v>
+        <v>5.7202</v>
       </c>
       <c r="D19" t="n">
-        <v>5.9075</v>
+        <v>5.7715</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9751</v>
+        <v>5.9151</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0027</v>
+        <v>6.0499</v>
       </c>
       <c r="G19" t="n">
-        <v>6.0823</v>
+        <v>6.2097</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6327</v>
+        <v>6.6379</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9478</v>
+        <v>6.9498</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2701</v>
+        <v>7.2695</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5723</v>
+        <v>7.5701</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8299</v>
+        <v>7.8275</v>
       </c>
       <c r="M19" t="n">
-        <v>8.019</v>
+        <v>8.0183</v>
       </c>
       <c r="N19" t="n">
-        <v>8.112500000000001</v>
+        <v>8.116</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0801</v>
+        <v>8.0907</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8909</v>
+        <v>7.9118</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6665</v>
+        <v>5.6627</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7561</v>
+        <v>5.8449</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8011</v>
+        <v>5.9075</v>
       </c>
       <c r="E20" t="n">
-        <v>5.8897</v>
+        <v>5.9751</v>
       </c>
       <c r="F20" t="n">
-        <v>5.9603</v>
+        <v>6.0027</v>
       </c>
       <c r="G20" t="n">
         <v>6.0823</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6259</v>
+        <v>6.6327</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9462</v>
+        <v>6.9478</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2729</v>
+        <v>7.2701</v>
       </c>
       <c r="K20" t="n">
-        <v>7.5783</v>
+        <v>7.5723</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8377</v>
+        <v>7.8299</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0267</v>
+        <v>8.019</v>
       </c>
       <c r="N20" t="n">
-        <v>8.117599999999999</v>
+        <v>8.112500000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0794</v>
+        <v>8.0801</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8808</v>
+        <v>7.8909</v>
       </c>
       <c r="Q20" t="n">
         <v>6.44</v>
@@ -1551,55 +1551,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.7242</v>
+        <v>5.6665</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7821</v>
+        <v>5.7561</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8221</v>
+        <v>5.8011</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9218</v>
+        <v>5.8897</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0112</v>
+        <v>5.9603</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1292</v>
+        <v>6.0823</v>
       </c>
       <c r="H21" t="n">
-        <v>6.592</v>
+        <v>6.6259</v>
       </c>
       <c r="I21" t="n">
-        <v>6.926</v>
+        <v>6.9462</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2639</v>
+        <v>7.2729</v>
       </c>
       <c r="K21" t="n">
         <v>7.5783</v>
       </c>
       <c r="L21" t="n">
+        <v>7.8377</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.0267</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.117599999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.0794</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.8808</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.7242</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.7821</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.8221</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.9218</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.0112</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.1292</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.592</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.926</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.2639</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.5783</v>
+      </c>
+      <c r="L22" t="n">
         <v>7.8443</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>8.0367</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>8.126799999999999</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>8.082700000000001</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>7.8723</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>6.45</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,218 +506,218 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N2" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O2" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P2" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C3" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E3" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F3" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G3" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J3" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N3" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C4" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F4" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M4" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N4" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F5" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G5" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M5" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q5" t="n">
         <v>6.43</v>
@@ -726,878 +726,878 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C6" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K6" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O6" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D7" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E7" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K7" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M7" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N7" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F8" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H8" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I8" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J8" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L8" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O8" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J9" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N9" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O9" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M10" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D11" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H11" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M11" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O11" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5.6597</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H12" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K12" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C13" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M13" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N13" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G14" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M14" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M15" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C16" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O16" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D17" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K17" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M17" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N17" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E18" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F18" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J18" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K18" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M18" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6625</v>
+        <v>5.5658</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7202</v>
+        <v>5.7355</v>
       </c>
       <c r="D19" t="n">
-        <v>5.7715</v>
+        <v>5.8092</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9151</v>
+        <v>5.931</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0499</v>
+        <v>6.017</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2097</v>
+        <v>6.1386</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6379</v>
+        <v>6.6308</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9498</v>
+        <v>6.9463</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2695</v>
+        <v>7.269</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5701</v>
+        <v>7.5719</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8275</v>
+        <v>7.8308</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0183</v>
+        <v>8.022</v>
       </c>
       <c r="N19" t="n">
-        <v>8.116</v>
+        <v>8.1187</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0907</v>
+        <v>8.0906</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9118</v>
+        <v>7.9068</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6627</v>
+        <v>5.6625</v>
       </c>
       <c r="C20" t="n">
-        <v>5.8449</v>
+        <v>5.7202</v>
       </c>
       <c r="D20" t="n">
-        <v>5.9075</v>
+        <v>5.7715</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9751</v>
+        <v>5.9151</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0027</v>
+        <v>6.0499</v>
       </c>
       <c r="G20" t="n">
-        <v>6.0823</v>
+        <v>6.2097</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6327</v>
+        <v>6.6379</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9478</v>
+        <v>6.9498</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2701</v>
+        <v>7.2695</v>
       </c>
       <c r="K20" t="n">
-        <v>7.5723</v>
+        <v>7.5701</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8299</v>
+        <v>7.8275</v>
       </c>
       <c r="M20" t="n">
-        <v>8.019</v>
+        <v>8.0183</v>
       </c>
       <c r="N20" t="n">
-        <v>8.112500000000001</v>
+        <v>8.116</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0801</v>
+        <v>8.0907</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8909</v>
+        <v>7.9118</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6665</v>
+        <v>5.6627</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7561</v>
+        <v>5.8449</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8011</v>
+        <v>5.9075</v>
       </c>
       <c r="E21" t="n">
-        <v>5.8897</v>
+        <v>5.9751</v>
       </c>
       <c r="F21" t="n">
-        <v>5.9603</v>
+        <v>6.0027</v>
       </c>
       <c r="G21" t="n">
         <v>6.0823</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6259</v>
+        <v>6.6327</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9462</v>
+        <v>6.9478</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2729</v>
+        <v>7.2701</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5783</v>
+        <v>7.5723</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8377</v>
+        <v>7.8299</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0267</v>
+        <v>8.019</v>
       </c>
       <c r="N21" t="n">
-        <v>8.117599999999999</v>
+        <v>8.112500000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0794</v>
+        <v>8.0801</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8808</v>
+        <v>7.8909</v>
       </c>
       <c r="Q21" t="n">
         <v>6.44</v>
@@ -1606,55 +1606,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.7242</v>
+        <v>5.6665</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7821</v>
+        <v>5.7561</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8221</v>
+        <v>5.8011</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9218</v>
+        <v>5.8897</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0112</v>
+        <v>5.9603</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1292</v>
+        <v>6.0823</v>
       </c>
       <c r="H22" t="n">
-        <v>6.592</v>
+        <v>6.6259</v>
       </c>
       <c r="I22" t="n">
-        <v>6.926</v>
+        <v>6.9462</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2639</v>
+        <v>7.2729</v>
       </c>
       <c r="K22" t="n">
         <v>7.5783</v>
       </c>
       <c r="L22" t="n">
+        <v>7.8377</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8.0267</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.117599999999999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>8.0794</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.8808</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.7242</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.7821</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.8221</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.9218</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.0112</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.1292</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.592</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.926</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7.2639</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7.5783</v>
+      </c>
+      <c r="L23" t="n">
         <v>7.8443</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>8.0367</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>8.126799999999999</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>8.082700000000001</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>7.8723</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>6.45</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,273 +506,273 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N2" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O2" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F3" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N3" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O3" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P3" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C4" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E4" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G4" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J4" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N4" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F5" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M5" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N5" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G6" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M6" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q6" t="n">
         <v>6.43</v>
@@ -781,878 +781,878 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C7" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K7" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O7" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D8" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E8" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F8" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J8" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K8" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M8" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N8" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F9" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H9" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I9" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J9" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L9" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O9" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N10" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O10" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M11" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D12" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H12" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M12" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O12" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5.6597</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H13" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K13" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C14" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M14" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N14" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G15" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M15" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M16" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O17" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D18" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K18" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M18" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N18" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E19" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F19" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J19" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M19" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6625</v>
+        <v>5.5658</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7202</v>
+        <v>5.7355</v>
       </c>
       <c r="D20" t="n">
-        <v>5.7715</v>
+        <v>5.8092</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9151</v>
+        <v>5.931</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0499</v>
+        <v>6.017</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2097</v>
+        <v>6.1386</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6379</v>
+        <v>6.6308</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9498</v>
+        <v>6.9463</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2695</v>
+        <v>7.269</v>
       </c>
       <c r="K20" t="n">
-        <v>7.5701</v>
+        <v>7.5719</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8275</v>
+        <v>7.8308</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0183</v>
+        <v>8.022</v>
       </c>
       <c r="N20" t="n">
-        <v>8.116</v>
+        <v>8.1187</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0907</v>
+        <v>8.0906</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9118</v>
+        <v>7.9068</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6627</v>
+        <v>5.6625</v>
       </c>
       <c r="C21" t="n">
-        <v>5.8449</v>
+        <v>5.7202</v>
       </c>
       <c r="D21" t="n">
-        <v>5.9075</v>
+        <v>5.7715</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9751</v>
+        <v>5.9151</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0027</v>
+        <v>6.0499</v>
       </c>
       <c r="G21" t="n">
-        <v>6.0823</v>
+        <v>6.2097</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6327</v>
+        <v>6.6379</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9478</v>
+        <v>6.9498</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2701</v>
+        <v>7.2695</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5723</v>
+        <v>7.5701</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8299</v>
+        <v>7.8275</v>
       </c>
       <c r="M21" t="n">
-        <v>8.019</v>
+        <v>8.0183</v>
       </c>
       <c r="N21" t="n">
-        <v>8.112500000000001</v>
+        <v>8.116</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0801</v>
+        <v>8.0907</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8909</v>
+        <v>7.9118</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.6665</v>
+        <v>5.6627</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7561</v>
+        <v>5.8449</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8011</v>
+        <v>5.9075</v>
       </c>
       <c r="E22" t="n">
-        <v>5.8897</v>
+        <v>5.9751</v>
       </c>
       <c r="F22" t="n">
-        <v>5.9603</v>
+        <v>6.0027</v>
       </c>
       <c r="G22" t="n">
         <v>6.0823</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6259</v>
+        <v>6.6327</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9462</v>
+        <v>6.9478</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2729</v>
+        <v>7.2701</v>
       </c>
       <c r="K22" t="n">
-        <v>7.5783</v>
+        <v>7.5723</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8377</v>
+        <v>7.8299</v>
       </c>
       <c r="M22" t="n">
-        <v>8.0267</v>
+        <v>8.019</v>
       </c>
       <c r="N22" t="n">
-        <v>8.117599999999999</v>
+        <v>8.112500000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>8.0794</v>
+        <v>8.0801</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8808</v>
+        <v>7.8909</v>
       </c>
       <c r="Q22" t="n">
         <v>6.44</v>
@@ -1661,56 +1661,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.7242</v>
+        <v>5.6665</v>
       </c>
       <c r="C23" t="n">
-        <v>5.7821</v>
+        <v>5.7561</v>
       </c>
       <c r="D23" t="n">
-        <v>5.8221</v>
+        <v>5.8011</v>
       </c>
       <c r="E23" t="n">
-        <v>5.9218</v>
+        <v>5.8897</v>
       </c>
       <c r="F23" t="n">
-        <v>6.0112</v>
+        <v>5.9603</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1292</v>
+        <v>6.0823</v>
       </c>
       <c r="H23" t="n">
-        <v>6.592</v>
+        <v>6.6259</v>
       </c>
       <c r="I23" t="n">
-        <v>6.926</v>
+        <v>6.9462</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2639</v>
+        <v>7.2729</v>
       </c>
       <c r="K23" t="n">
         <v>7.5783</v>
       </c>
       <c r="L23" t="n">
-        <v>7.8443</v>
+        <v>7.8377</v>
       </c>
       <c r="M23" t="n">
-        <v>8.0367</v>
+        <v>8.0267</v>
       </c>
       <c r="N23" t="n">
-        <v>8.126799999999999</v>
+        <v>8.117599999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>8.082700000000001</v>
+        <v>8.0794</v>
       </c>
       <c r="P23" t="n">
-        <v>7.8723</v>
+        <v>7.8808</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,53 +506,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E2" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N2" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O2" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q2" t="n">
         <v>6.47</v>
@@ -561,273 +561,273 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F3" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M3" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N3" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O3" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N4" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O4" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P4" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E5" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F5" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G5" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J5" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N5" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F6" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M6" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N6" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G7" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M7" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q7" t="n">
         <v>6.43</v>
@@ -836,881 +836,771 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C8" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J8" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K8" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O8" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D9" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E9" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F9" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J9" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K9" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M9" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N9" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F10" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H10" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I10" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L10" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O10" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N11" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O11" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M12" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D13" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H13" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M13" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O13" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5.6597</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H14" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K14" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C15" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M15" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N15" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G16" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M16" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M17" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O18" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D19" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K19" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M19" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N19" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E20" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F20" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J20" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K20" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M20" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6625</v>
+        <v>5.5658</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7202</v>
+        <v>5.7355</v>
       </c>
       <c r="D21" t="n">
-        <v>5.7715</v>
+        <v>5.8092</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9151</v>
+        <v>5.931</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0499</v>
+        <v>6.017</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2097</v>
+        <v>6.1386</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6379</v>
+        <v>6.6308</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9498</v>
+        <v>6.9463</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2695</v>
+        <v>7.269</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5701</v>
+        <v>7.5719</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8275</v>
+        <v>7.8308</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0183</v>
+        <v>8.022</v>
       </c>
       <c r="N21" t="n">
-        <v>8.116</v>
+        <v>8.1187</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0907</v>
+        <v>8.0906</v>
       </c>
       <c r="P21" t="n">
-        <v>7.9118</v>
+        <v>7.9068</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.6627</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.8449</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.9075</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.9751</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.0027</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.0823</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.6327</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6.9478</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7.2701</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.5723</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.8299</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8.019</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.112500000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.0801</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.8909</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5.6665</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.7561</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5.8011</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.8897</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5.9603</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.0823</v>
-      </c>
-      <c r="H23" t="n">
-        <v>6.6259</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6.9462</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7.2729</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.5783</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.8377</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.0267</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8.117599999999999</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.0794</v>
-      </c>
-      <c r="P23" t="n">
-        <v>7.8808</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,108 +506,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L2" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N2" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O2" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E3" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M3" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N3" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O3" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q3" t="n">
         <v>6.47</v>
@@ -616,273 +616,273 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N4" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O4" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F5" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N5" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O5" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P5" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E6" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G6" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J6" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N6" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F7" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M7" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N7" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F8" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G8" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M8" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q8" t="n">
         <v>6.43</v>
@@ -891,716 +891,716 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C9" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J9" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K9" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O9" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D10" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E10" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F10" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H10" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K10" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M10" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N10" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F11" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H11" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I11" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L11" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O11" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N12" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O12" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M13" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D14" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H14" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M14" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O14" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>5.6597</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H15" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K15" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C16" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M16" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N16" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G17" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M17" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M18" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O19" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D20" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K20" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M20" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N20" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.5658</v>
+        <v>5.7014</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7355</v>
+        <v>5.7526</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8092</v>
+        <v>5.7935</v>
       </c>
       <c r="E21" t="n">
-        <v>5.931</v>
+        <v>5.9029</v>
       </c>
       <c r="F21" t="n">
-        <v>6.017</v>
+        <v>6.0038</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1386</v>
+        <v>6.1457</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6308</v>
+        <v>6.6348</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9463</v>
+        <v>6.9483</v>
       </c>
       <c r="J21" t="n">
-        <v>7.269</v>
+        <v>7.2694</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5719</v>
+        <v>7.571</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8308</v>
+        <v>7.8289</v>
       </c>
       <c r="M21" t="n">
-        <v>8.022</v>
+        <v>8.019600000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1187</v>
+        <v>8.116300000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0906</v>
+        <v>8.089</v>
       </c>
       <c r="P21" t="n">
-        <v>7.9068</v>
+        <v>7.9069</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,163 +506,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J2" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P2" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C3" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F3" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L3" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M3" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N3" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O3" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E4" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N4" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O4" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q4" t="n">
         <v>6.47</v>
@@ -671,273 +671,273 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F5" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O5" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N6" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O6" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E7" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G7" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J7" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N7" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C8" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F8" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M8" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N8" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F9" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G9" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M9" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q9" t="n">
         <v>6.43</v>
@@ -946,660 +946,715 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C10" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K10" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O10" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D11" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E11" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K11" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M11" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N11" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F12" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H12" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I12" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L12" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O12" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N13" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M14" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D15" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H15" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M15" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O15" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>5.6597</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H16" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K16" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C17" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M17" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N17" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G18" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M18" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M19" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C20" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O20" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.7026</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.8305</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.8868</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.9829</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.0525</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.1584</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.6491</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.9724</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.3019</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.6088</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.8671</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.0512</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.132300000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.078200000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.8572</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>5.7014</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5.7526</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>5.7935</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>5.9029</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>6.0038</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6.1457</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>6.6348</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>6.9483</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>7.2694</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>7.571</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>7.8289</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>8.019600000000001</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>8.116300000000001</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>8.089</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>7.9069</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>6.42</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,218 +506,218 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D2" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E2" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F2" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M2" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C3" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J3" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M3" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P3" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C4" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L4" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N4" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O4" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E5" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O5" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q5" t="n">
         <v>6.47</v>
@@ -726,273 +726,273 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N6" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O6" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N7" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O7" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C8" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E8" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G8" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J8" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N8" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F9" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M9" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N9" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F10" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G10" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M10" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q10" t="n">
         <v>6.43</v>
@@ -1001,660 +1001,715 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C11" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J11" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K11" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O11" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D12" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E12" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K12" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M12" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N12" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F13" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H13" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I13" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L13" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N14" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M15" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D16" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H16" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M16" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O16" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>5.6597</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H17" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K17" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C18" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M18" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N18" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G19" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M19" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M20" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C21" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O21" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.7026</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.8305</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.8868</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.9829</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.0525</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.1584</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.6491</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.9724</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.3019</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.6088</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.8671</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8.0512</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.132300000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>8.078200000000001</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.8572</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>5.7014</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>5.7526</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>5.7935</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>5.9029</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>6.0038</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>6.1457</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>6.6348</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>6.9483</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>7.2694</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>7.571</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>7.8289</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>8.019600000000001</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>8.116300000000001</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>8.089</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>7.9069</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>6.42</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,273 +506,273 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M2" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O2" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D3" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E3" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F3" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M3" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C4" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J4" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P4" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F5" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L5" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O5" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P5" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E6" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N6" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O6" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q6" t="n">
         <v>6.47</v>
@@ -781,273 +781,273 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O7" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N8" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E9" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G9" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J9" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N9" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C10" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F10" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H10" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M10" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N10" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G11" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M11" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q11" t="n">
         <v>6.43</v>
@@ -1056,661 +1056,661 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C12" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J12" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K12" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O12" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E13" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F13" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M13" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N13" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F14" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H14" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I14" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L14" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N15" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M16" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D17" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H17" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M17" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O17" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>5.6597</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H18" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K18" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C19" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M19" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N19" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G20" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M20" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M21" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.7026</v>
+        <v>5.6556</v>
       </c>
       <c r="C22" t="n">
-        <v>5.8305</v>
+        <v>5.7992</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8868</v>
+        <v>5.8625</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9829</v>
+        <v>5.9705</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0525</v>
+        <v>6.0487</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1584</v>
+        <v>6.1539</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6491</v>
+        <v>6.6245</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9724</v>
+        <v>6.9589</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3019</v>
+        <v>7.2975</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6088</v>
+        <v>7.6116</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8671</v>
+        <v>7.8747</v>
       </c>
       <c r="M22" t="n">
-        <v>8.0512</v>
+        <v>8.060600000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>8.132300000000001</v>
+        <v>8.1396</v>
       </c>
       <c r="O22" t="n">
-        <v>8.078200000000001</v>
+        <v>8.0785</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8572</v>
+        <v>7.8451</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.7014</v>
+        <v>5.7026</v>
       </c>
       <c r="C23" t="n">
-        <v>5.7526</v>
+        <v>5.8305</v>
       </c>
       <c r="D23" t="n">
-        <v>5.7935</v>
+        <v>5.8868</v>
       </c>
       <c r="E23" t="n">
-        <v>5.9029</v>
+        <v>5.9829</v>
       </c>
       <c r="F23" t="n">
-        <v>6.0038</v>
+        <v>6.0525</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1457</v>
+        <v>6.1584</v>
       </c>
       <c r="H23" t="n">
-        <v>6.6348</v>
+        <v>6.6491</v>
       </c>
       <c r="I23" t="n">
-        <v>6.9483</v>
+        <v>6.9724</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2694</v>
+        <v>7.3019</v>
       </c>
       <c r="K23" t="n">
-        <v>7.571</v>
+        <v>7.6088</v>
       </c>
       <c r="L23" t="n">
-        <v>7.8289</v>
+        <v>7.8671</v>
       </c>
       <c r="M23" t="n">
-        <v>8.019600000000001</v>
+        <v>8.0512</v>
       </c>
       <c r="N23" t="n">
-        <v>8.116300000000001</v>
+        <v>8.132300000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>8.089</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>7.9069</v>
+        <v>7.8572</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.42</v>
+        <v>6.45</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,328 +506,328 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D2" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L2" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M2" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N2" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P2" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M3" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O3" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D4" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E4" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F4" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M4" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J5" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P5" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L6" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N6" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O6" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P6" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E7" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O7" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q7" t="n">
         <v>6.47</v>
@@ -836,273 +836,273 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N9" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C10" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E10" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G10" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H10" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J10" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N10" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C11" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F11" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M11" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N11" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G12" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M12" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q12" t="n">
         <v>6.43</v>
@@ -1111,606 +1111,551 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C13" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O13" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E14" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F14" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K14" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M14" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N14" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F15" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H15" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I15" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L15" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N16" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M17" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D18" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H18" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M18" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O18" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>5.6597</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H19" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K19" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C20" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M20" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N20" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G21" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M21" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.6556</v>
+        <v>5.6053</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7992</v>
+        <v>5.7813</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8625</v>
+        <v>5.8591</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9705</v>
+        <v>5.9909</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0487</v>
+        <v>6.0861</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1539</v>
+        <v>6.198</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6245</v>
+        <v>6.6317</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9589</v>
+        <v>6.9615</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2975</v>
+        <v>7.2964</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6116</v>
+        <v>7.6083</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8747</v>
+        <v>7.8715</v>
       </c>
       <c r="M22" t="n">
-        <v>8.060600000000001</v>
+        <v>8.060499999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.1396</v>
+        <v>8.1463</v>
       </c>
       <c r="O22" t="n">
-        <v>8.0785</v>
+        <v>8.0968</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8451</v>
+        <v>7.8797</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5.7026</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.8305</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5.8868</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.9829</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.0525</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.1584</v>
-      </c>
-      <c r="H23" t="n">
-        <v>6.6491</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6.9724</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7.3019</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.6088</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.8671</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.0512</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8.132300000000001</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.078200000000001</v>
-      </c>
-      <c r="P23" t="n">
-        <v>7.8572</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,383 +506,383 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L2" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P2" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C3" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D3" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L3" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M3" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N3" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P3" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M4" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O4" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C5" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D5" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E5" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F5" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M5" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J6" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L7" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O7" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P7" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E8" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O8" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q8" t="n">
         <v>6.47</v>
@@ -891,273 +891,273 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N10" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C11" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E11" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G11" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J11" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N11" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F12" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M12" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N12" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F13" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G13" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M13" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q13" t="n">
         <v>6.43</v>
@@ -1166,496 +1166,496 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C14" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J14" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K14" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O14" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E15" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F15" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H15" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K15" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M15" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N15" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F16" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H16" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I16" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L16" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N17" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M18" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D19" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H19" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M19" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O19" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>5.6597</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H20" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K20" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C21" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M21" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N21" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.6053</v>
+        <v>5.7432</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7813</v>
+        <v>5.794</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8591</v>
+        <v>5.8375</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9909</v>
+        <v>5.9579</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0861</v>
+        <v>6.0705</v>
       </c>
       <c r="G22" t="n">
-        <v>6.198</v>
+        <v>6.2039</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6317</v>
+        <v>6.6311</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9615</v>
+        <v>6.9608</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2964</v>
+        <v>7.2956</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6083</v>
+        <v>7.6076</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8715</v>
+        <v>7.8711</v>
       </c>
       <c r="M22" t="n">
-        <v>8.060499999999999</v>
+        <v>8.061</v>
       </c>
       <c r="N22" t="n">
-        <v>8.1463</v>
+        <v>8.148300000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>8.0968</v>
+        <v>8.1008</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8797</v>
+        <v>7.8865</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,438 +506,438 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E2" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M2" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L3" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M3" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P3" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C4" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D4" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L4" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M4" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N4" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P4" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L5" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M5" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O5" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D6" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E6" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F6" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M6" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D7" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J7" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C8" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L8" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P8" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E9" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O9" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q9" t="n">
         <v>6.47</v>
@@ -946,273 +946,273 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N11" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E12" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G12" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H12" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J12" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M12" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N12" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C13" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F13" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M13" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N13" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F14" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M14" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q14" t="n">
         <v>6.43</v>
@@ -1221,440 +1221,495 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C15" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K15" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O15" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E16" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F16" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H16" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K16" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M16" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N16" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F17" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H17" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I17" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L17" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N18" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M19" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D20" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H20" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M20" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O20" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>5.6597</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H21" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K21" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O21" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.6597</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.7699</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.8263</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.9395</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.0309</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.1524</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.9627</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.3001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.614</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.8787</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8.0686</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.154400000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>8.1035</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.8837</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>31/08/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>5.7432</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>5.794</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>5.8375</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>5.9579</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>6.0705</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>6.2039</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>6.6311</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>6.9608</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>7.2956</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>7.6076</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>7.8711</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>8.061</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>8.148300000000001</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>8.1008</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>7.8865</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>6.46</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,493 +506,493 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K2" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M2" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O2" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P2" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E3" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M3" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L4" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M4" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P4" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C5" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D5" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L5" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M5" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P5" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M6" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O6" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D7" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E7" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F7" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M7" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C8" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J8" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L9" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O9" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E10" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O10" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q10" t="n">
         <v>6.47</v>
@@ -1001,273 +1001,273 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M12" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N12" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C13" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E13" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G13" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J13" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N13" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F14" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M14" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N14" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F15" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G15" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M15" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q15" t="n">
         <v>6.43</v>
@@ -1276,441 +1276,441 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C16" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K16" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O16" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D17" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E17" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F17" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H17" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M17" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N17" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F18" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H18" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I18" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L18" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N19" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M20" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D21" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H21" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M21" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O21" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>5.6597</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H22" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K22" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M22" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O22" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.7432</v>
+        <v>5.6597</v>
       </c>
       <c r="C23" t="n">
-        <v>5.794</v>
+        <v>5.7699</v>
       </c>
       <c r="D23" t="n">
-        <v>5.8375</v>
+        <v>5.8263</v>
       </c>
       <c r="E23" t="n">
-        <v>5.9579</v>
+        <v>5.9395</v>
       </c>
       <c r="F23" t="n">
-        <v>6.0705</v>
+        <v>6.0309</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2039</v>
+        <v>6.1524</v>
       </c>
       <c r="H23" t="n">
-        <v>6.6311</v>
+        <v>6.63</v>
       </c>
       <c r="I23" t="n">
-        <v>6.9608</v>
+        <v>6.9627</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2956</v>
+        <v>7.3001</v>
       </c>
       <c r="K23" t="n">
-        <v>7.6076</v>
+        <v>7.614</v>
       </c>
       <c r="L23" t="n">
-        <v>7.8711</v>
+        <v>7.8787</v>
       </c>
       <c r="M23" t="n">
-        <v>8.061</v>
+        <v>8.0686</v>
       </c>
       <c r="N23" t="n">
-        <v>8.148300000000001</v>
+        <v>8.154400000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>8.1008</v>
+        <v>8.1035</v>
       </c>
       <c r="P23" t="n">
-        <v>7.8865</v>
+        <v>7.8837</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,548 +506,548 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H2" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J2" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L2" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K3" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M3" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O3" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P3" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E4" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M4" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L5" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P5" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D6" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L6" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M6" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N6" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P6" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M7" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O7" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D8" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E8" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F8" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M8" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D9" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J9" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C10" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F10" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L10" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O10" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E11" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O11" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q11" t="n">
         <v>6.47</v>
@@ -1056,273 +1056,273 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N13" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E14" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G14" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J14" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M14" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N14" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C15" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F15" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H15" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M15" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N15" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F16" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G16" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M16" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q16" t="n">
         <v>6.43</v>
@@ -1331,386 +1331,386 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C17" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O17" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D18" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E18" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F18" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H18" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K18" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M18" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N18" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F19" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H19" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I19" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L19" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N20" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.5812</v>
+        <v>5.5648</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7494</v>
+        <v>5.7404</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8265</v>
+        <v>5.8203</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9644</v>
+        <v>5.9618</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0679</v>
+        <v>6.0673</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1865</v>
+        <v>6.1853</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6206</v>
+        <v>6.6141</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9566</v>
+        <v>6.9531</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2965</v>
+        <v>7.2956</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6116</v>
+        <v>7.6126</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8756</v>
+        <v>7.8778</v>
       </c>
       <c r="M21" t="n">
-        <v>8.062099999999999</v>
+        <v>8.0646</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1411</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>8.079700000000001</v>
+        <v>8.0792</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8452</v>
+        <v>7.8407</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.6597</v>
+        <v>5.5812</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7942</v>
+        <v>5.7494</v>
       </c>
       <c r="D22" t="n">
-        <v>5.855</v>
+        <v>5.8265</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9618</v>
+        <v>5.9644</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0409</v>
+        <v>6.0679</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1463</v>
+        <v>6.1865</v>
       </c>
       <c r="H22" t="n">
-        <v>6.62</v>
+        <v>6.6206</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9608</v>
+        <v>6.9566</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3049</v>
+        <v>7.2965</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6231</v>
+        <v>7.6116</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8888</v>
+        <v>7.8756</v>
       </c>
       <c r="M22" t="n">
-        <v>8.075100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.1515</v>
+        <v>8.1411</v>
       </c>
       <c r="O22" t="n">
-        <v>8.084300000000001</v>
+        <v>8.079700000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8404</v>
+        <v>7.8452</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>5.6597</v>
       </c>
       <c r="C23" t="n">
-        <v>5.7699</v>
+        <v>5.7942</v>
       </c>
       <c r="D23" t="n">
-        <v>5.8263</v>
+        <v>5.855</v>
       </c>
       <c r="E23" t="n">
-        <v>5.9395</v>
+        <v>5.9618</v>
       </c>
       <c r="F23" t="n">
-        <v>6.0309</v>
+        <v>6.0409</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1524</v>
+        <v>6.1463</v>
       </c>
       <c r="H23" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="I23" t="n">
-        <v>6.9627</v>
+        <v>6.9608</v>
       </c>
       <c r="J23" t="n">
-        <v>7.3001</v>
+        <v>7.3049</v>
       </c>
       <c r="K23" t="n">
-        <v>7.614</v>
+        <v>7.6231</v>
       </c>
       <c r="L23" t="n">
-        <v>7.8787</v>
+        <v>7.8888</v>
       </c>
       <c r="M23" t="n">
-        <v>8.0686</v>
+        <v>8.075100000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>8.154400000000001</v>
+        <v>8.1515</v>
       </c>
       <c r="O23" t="n">
-        <v>8.1035</v>
+        <v>8.084300000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>7.8837</v>
+        <v>7.8404</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,603 +506,603 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F2" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G2" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O2" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H3" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J3" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L3" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K4" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M4" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O4" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P4" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E5" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M5" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L6" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M6" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P6" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C7" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D7" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L7" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M7" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N7" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P7" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L8" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M8" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O8" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C9" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D9" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E9" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F9" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M9" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C10" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D10" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J10" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C11" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F11" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I11" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L11" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P11" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E12" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O12" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q12" t="n">
         <v>6.47</v>
@@ -1111,273 +1111,273 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M14" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N14" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C15" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E15" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G15" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H15" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J15" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M15" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N15" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C16" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F16" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H16" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M16" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N16" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F17" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G17" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M17" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q17" t="n">
         <v>6.43</v>
@@ -1386,330 +1386,220 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C18" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K18" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O18" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D19" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E19" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F19" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H19" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M19" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N19" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F20" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H20" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I20" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L20" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.5648</v>
+        <v>5.7363</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7404</v>
+        <v>5.7863</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8203</v>
+        <v>5.8293</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9618</v>
+        <v>5.9485</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0673</v>
+        <v>6.06</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1853</v>
+        <v>6.1887</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6141</v>
+        <v>6.613</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9531</v>
+        <v>6.953</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2956</v>
+        <v>7.2962</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6126</v>
+        <v>7.6135</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8778</v>
+        <v>7.878</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0646</v>
+        <v>8.0631</v>
       </c>
       <c r="N21" t="n">
-        <v>8.142899999999999</v>
+        <v>8.1381</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0792</v>
+        <v>8.0695</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8407</v>
+        <v>7.8244</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.5812</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.7494</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.8265</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.9644</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.0679</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.1865</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.6206</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6.9566</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7.2965</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.6116</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.8756</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8.062099999999999</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.1411</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.079700000000001</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.8452</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5.6597</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.7942</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5.855</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.9618</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.0409</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.1463</v>
-      </c>
-      <c r="H23" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6.9608</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7.3049</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.6231</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.8888</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.075100000000001</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8.1515</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.084300000000001</v>
-      </c>
-      <c r="P23" t="n">
-        <v>7.8404</v>
-      </c>
-      <c r="Q23" t="n">
         <v>6.43</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,658 +506,658 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F2" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J2" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M2" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O2" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F3" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G3" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O3" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P3" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H4" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J4" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L4" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K5" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M5" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O5" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P5" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E6" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M6" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L7" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M7" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P7" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C8" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D8" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L8" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M8" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N8" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P8" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M9" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O9" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C10" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D10" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E10" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F10" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M10" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C11" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D11" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J11" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I12" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L12" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E13" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O13" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q13" t="n">
         <v>6.47</v>
@@ -1166,273 +1166,273 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M15" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N15" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C16" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E16" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G16" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H16" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J16" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M16" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N16" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F17" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H17" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M17" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N17" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F18" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G18" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M18" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q18" t="n">
         <v>6.43</v>
@@ -1441,165 +1441,220 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C19" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J19" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K19" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O19" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D20" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E20" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F20" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H20" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K20" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M20" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N20" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.6626</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.7058</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.7455</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.858</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.9638</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.1041</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.5973</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.9373</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.2804</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.5993</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.8687</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.063000000000001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.153</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.8892</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>5.7363</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5.7863</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>5.8293</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>5.9485</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>6.06</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6.1887</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>6.613</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>6.953</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>7.2962</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>7.6135</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>7.878</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>8.0631</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>8.1381</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>8.0695</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>7.8244</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>6.43</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,713 +506,713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C2" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M2" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P2" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F3" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J3" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M3" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O3" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G4" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O4" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P4" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H5" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J5" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L5" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K6" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M6" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O6" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P6" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E7" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M7" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L8" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M8" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P8" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C9" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D9" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L9" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M9" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N9" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P9" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L10" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M10" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O10" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C11" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D11" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E11" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F11" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M11" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J12" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C13" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L13" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O13" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E14" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O14" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q14" t="n">
         <v>6.47</v>
@@ -1221,273 +1221,273 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M16" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N16" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E17" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G17" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H17" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J17" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M17" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N17" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F18" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H18" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M18" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N18" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F19" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G19" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M19" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q19" t="n">
         <v>6.43</v>
@@ -1496,165 +1496,220 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C20" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K20" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O20" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D21" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E21" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F21" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H21" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M21" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N21" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.6626</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.7058</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.7455</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.858</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.9638</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.1041</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.5973</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.9373</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.2804</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.5993</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.8687</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8.063000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.153</v>
+      </c>
+      <c r="O22" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.8892</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>5.7363</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>5.7863</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>5.8293</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>5.9485</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>6.06</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>6.1887</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>6.613</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>6.953</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>7.2962</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>7.6135</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>7.878</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>8.0631</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>8.1381</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>8.0695</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>7.8244</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>6.43</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,53 +506,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P2" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q2" t="n">
         <v>6.57</v>
@@ -561,713 +561,713 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C3" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M3" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P3" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F4" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J4" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M4" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O4" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F5" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G5" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O5" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P5" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H6" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J6" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L6" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K7" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M7" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O7" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P7" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E8" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M8" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L9" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M9" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P9" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C10" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D10" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L10" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M10" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N10" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P10" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L11" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M11" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O11" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C12" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D12" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E12" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F12" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M12" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C13" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J13" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I14" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L14" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O14" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P14" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E15" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O15" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q15" t="n">
         <v>6.47</v>
@@ -1276,273 +1276,273 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M17" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N17" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E18" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G18" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H18" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J18" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M18" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N18" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F19" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H19" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M19" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N19" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F20" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G20" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M20" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q20" t="n">
         <v>6.43</v>
@@ -1551,166 +1551,166 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C21" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J21" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K21" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O21" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P21" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D22" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E22" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F22" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H22" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K22" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M22" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N22" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.7363</v>
+        <v>5.6626</v>
       </c>
       <c r="C23" t="n">
-        <v>5.7863</v>
+        <v>5.7058</v>
       </c>
       <c r="D23" t="n">
-        <v>5.8293</v>
+        <v>5.7455</v>
       </c>
       <c r="E23" t="n">
-        <v>5.9485</v>
+        <v>5.858</v>
       </c>
       <c r="F23" t="n">
-        <v>6.06</v>
+        <v>5.9638</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1887</v>
+        <v>6.1041</v>
       </c>
       <c r="H23" t="n">
-        <v>6.613</v>
+        <v>6.5973</v>
       </c>
       <c r="I23" t="n">
-        <v>6.953</v>
+        <v>6.9373</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2962</v>
+        <v>7.2804</v>
       </c>
       <c r="K23" t="n">
-        <v>7.6135</v>
+        <v>7.5993</v>
       </c>
       <c r="L23" t="n">
-        <v>7.878</v>
+        <v>7.8687</v>
       </c>
       <c r="M23" t="n">
-        <v>8.0631</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>8.1381</v>
+        <v>8.153</v>
       </c>
       <c r="O23" t="n">
-        <v>8.0695</v>
+        <v>8.106</v>
       </c>
       <c r="P23" t="n">
-        <v>7.8244</v>
+        <v>7.8892</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,53 +506,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H2" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L2" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M2" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q2" t="n">
         <v>6.57</v>
@@ -561,53 +561,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P3" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q3" t="n">
         <v>6.57</v>
@@ -616,713 +616,713 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C4" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M4" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P4" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F5" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J5" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M5" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O5" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F6" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G6" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O6" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P6" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H7" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J7" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L7" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K8" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M8" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O8" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P8" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E9" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M9" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L10" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M10" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P10" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C11" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D11" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L11" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M11" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N11" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P11" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L12" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M12" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O12" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C13" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D13" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E13" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F13" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M13" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J14" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C15" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L15" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O15" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P15" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E16" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O16" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q16" t="n">
         <v>6.47</v>
@@ -1331,273 +1331,273 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M18" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N18" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E19" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G19" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H19" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J19" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M19" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N19" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.67</v>
+        <v>5.7721</v>
       </c>
       <c r="C20" t="n">
-        <v>5.8044</v>
+        <v>5.8123</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8638</v>
+        <v>5.8455</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9653</v>
+        <v>5.936</v>
       </c>
       <c r="F20" t="n">
-        <v>6.039</v>
+        <v>6.0201</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1294</v>
+        <v>6.128</v>
       </c>
       <c r="H20" t="n">
-        <v>6.5855</v>
+        <v>6.5944</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9448</v>
+        <v>6.9528</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3046</v>
+        <v>7.312</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6372</v>
+        <v>7.6441</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9164</v>
+        <v>7.9228</v>
       </c>
       <c r="M20" t="n">
-        <v>8.115399999999999</v>
+        <v>8.1214</v>
       </c>
       <c r="N20" t="n">
-        <v>8.203099999999999</v>
+        <v>8.208500000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1447</v>
+        <v>8.1495</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9062</v>
+        <v>7.9102</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.6567</v>
+        <v>5.67</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7963</v>
+        <v>5.8044</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8509</v>
+        <v>5.8638</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9285</v>
+        <v>5.9653</v>
       </c>
       <c r="F21" t="n">
-        <v>5.9761</v>
+        <v>6.039</v>
       </c>
       <c r="G21" t="n">
-        <v>6.0631</v>
+        <v>6.1294</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6006</v>
+        <v>6.5855</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9533</v>
+        <v>6.9448</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3076</v>
+        <v>7.3046</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6359</v>
+        <v>7.6372</v>
       </c>
       <c r="L21" t="n">
-        <v>7.9122</v>
+        <v>7.9164</v>
       </c>
       <c r="M21" t="n">
-        <v>8.110099999999999</v>
+        <v>8.115399999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.199</v>
+        <v>8.203099999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>8.1448</v>
+        <v>8.1447</v>
       </c>
       <c r="P21" t="n">
-        <v>7.9138</v>
+        <v>7.9062</v>
       </c>
       <c r="Q21" t="n">
         <v>6.43</v>
@@ -1606,111 +1606,111 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.6252</v>
+        <v>5.6567</v>
       </c>
       <c r="C22" t="n">
-        <v>5.792</v>
+        <v>5.7963</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8583</v>
+        <v>5.8509</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9558</v>
+        <v>5.9285</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0178</v>
+        <v>5.9761</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1159</v>
+        <v>6.0631</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6206</v>
+        <v>6.6006</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9499</v>
+        <v>6.9533</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2842</v>
+        <v>7.3076</v>
       </c>
       <c r="K22" t="n">
-        <v>7.5962</v>
+        <v>7.6359</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8609</v>
+        <v>7.9122</v>
       </c>
       <c r="M22" t="n">
-        <v>8.0533</v>
+        <v>8.110099999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.145300000000001</v>
+        <v>8.199</v>
       </c>
       <c r="O22" t="n">
-        <v>8.105</v>
+        <v>8.1448</v>
       </c>
       <c r="P22" t="n">
-        <v>7.9003</v>
+        <v>7.9138</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.42</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.6626</v>
+        <v>5.6252</v>
       </c>
       <c r="C23" t="n">
-        <v>5.7058</v>
+        <v>5.792</v>
       </c>
       <c r="D23" t="n">
-        <v>5.7455</v>
+        <v>5.8583</v>
       </c>
       <c r="E23" t="n">
-        <v>5.858</v>
+        <v>5.9558</v>
       </c>
       <c r="F23" t="n">
-        <v>5.9638</v>
+        <v>6.0178</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1041</v>
+        <v>6.1159</v>
       </c>
       <c r="H23" t="n">
-        <v>6.5973</v>
+        <v>6.6206</v>
       </c>
       <c r="I23" t="n">
-        <v>6.9373</v>
+        <v>6.9499</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2804</v>
+        <v>7.2842</v>
       </c>
       <c r="K23" t="n">
-        <v>7.5993</v>
+        <v>7.5962</v>
       </c>
       <c r="L23" t="n">
-        <v>7.8687</v>
+        <v>7.8609</v>
       </c>
       <c r="M23" t="n">
-        <v>8.063000000000001</v>
+        <v>8.0533</v>
       </c>
       <c r="N23" t="n">
-        <v>8.153</v>
+        <v>8.145300000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>8.106</v>
+        <v>8.105</v>
       </c>
       <c r="P23" t="n">
-        <v>7.8892</v>
+        <v>7.9003</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1548,171 +1548,6 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="C21" t="n">
-        <v>5.8044</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5.8638</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5.9653</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.039</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.1294</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6.5855</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6.9448</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7.3046</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.6372</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.9164</v>
-      </c>
-      <c r="M21" t="n">
-        <v>8.115399999999999</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8.203099999999999</v>
-      </c>
-      <c r="O21" t="n">
-        <v>8.1447</v>
-      </c>
-      <c r="P21" t="n">
-        <v>7.9062</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.43</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.6567</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.7963</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.8509</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.9285</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5.9761</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.0631</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.6006</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6.9533</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7.3076</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.6359</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.9122</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8.110099999999999</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.199</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.1448</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.9138</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5.6252</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.792</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5.8583</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.9558</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.0178</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.1159</v>
-      </c>
-      <c r="H23" t="n">
-        <v>6.6206</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6.9499</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7.2842</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.5962</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.8609</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.0533</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8.145300000000001</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8.105</v>
-      </c>
-      <c r="P23" t="n">
-        <v>7.9003</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.42</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,108 +506,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G2" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K2" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M2" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N2" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H3" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L3" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M3" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P3" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q3" t="n">
         <v>6.57</v>
@@ -616,53 +616,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P4" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q4" t="n">
         <v>6.57</v>
@@ -671,713 +671,713 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C5" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M5" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P5" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F6" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J6" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M6" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O6" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F7" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G7" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O7" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P7" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H8" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J8" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L8" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K9" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M9" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O9" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P9" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E10" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M10" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L11" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M11" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P11" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D12" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L12" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M12" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N12" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P12" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M13" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O13" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C14" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D14" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E14" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F14" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M14" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C15" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J15" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C16" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L16" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P16" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E17" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O17" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q17" t="n">
         <v>6.47</v>
@@ -1386,165 +1386,220 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E19" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M19" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N19" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.7266</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.7747</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.8124</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.9126</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.0048</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.1281</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.6195</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.9724</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.3271</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.6552</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.9299</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8.1242</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.206799999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.1431</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7.8991</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>5.7721</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>5.8123</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>5.8455</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>5.936</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>6.0201</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>6.128</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>6.5944</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>6.9528</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>7.312</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>7.6441</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>7.9228</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>8.1214</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>8.208500000000001</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>8.1495</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>7.9102</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>6.45</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,163 +506,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C2" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O2" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G3" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K3" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M3" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N3" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H4" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L4" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M4" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P4" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q4" t="n">
         <v>6.57</v>
@@ -671,53 +671,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P5" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q5" t="n">
         <v>6.57</v>
@@ -726,713 +726,713 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C6" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M6" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P6" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F7" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J7" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M7" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O7" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F8" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G8" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O8" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P8" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E9" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H9" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J9" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L9" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K10" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M10" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O10" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P10" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E11" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M11" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L12" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M12" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P12" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C13" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D13" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L13" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M13" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N13" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P13" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M14" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O14" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C15" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D15" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E15" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F15" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M15" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C16" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J16" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I17" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L17" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P17" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E18" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O18" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q18" t="n">
         <v>6.47</v>
@@ -1441,165 +1441,220 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D19" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M20" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N20" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.7266</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.7747</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.8124</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.9126</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.0048</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.1281</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.6195</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.9724</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.3271</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.6552</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.9299</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.1242</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.206799999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.1431</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.8991</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>5.7721</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5.8123</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>5.8455</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>5.936</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>6.0201</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6.128</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>6.5944</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>6.9528</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>7.312</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>7.6441</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>7.9228</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>8.1214</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>8.208500000000001</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>8.1495</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>7.9102</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>6.45</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,218 +506,218 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C2" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L2" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P2" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C3" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O3" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P3" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G4" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K4" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M4" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N4" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H5" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L5" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M5" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P5" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q5" t="n">
         <v>6.57</v>
@@ -726,53 +726,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P6" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q6" t="n">
         <v>6.57</v>
@@ -781,713 +781,713 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C7" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M7" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P7" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F8" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J8" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M8" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O8" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E9" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F9" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G9" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O9" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P9" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H10" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J10" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L10" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K11" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M11" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O11" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P11" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E12" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M12" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L13" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M13" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P13" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C14" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D14" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L14" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M14" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N14" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P14" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L15" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M15" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O15" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C16" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D16" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E16" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F16" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M16" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J17" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L18" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O18" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P18" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E19" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O19" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q19" t="n">
         <v>6.47</v>
@@ -1496,166 +1496,166 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C20" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D20" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D21" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E21" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L21" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M21" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N21" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O21" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.7721</v>
+        <v>5.7266</v>
       </c>
       <c r="C22" t="n">
-        <v>5.8123</v>
+        <v>5.7747</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8455</v>
+        <v>5.8124</v>
       </c>
       <c r="E22" t="n">
-        <v>5.936</v>
+        <v>5.9126</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0201</v>
+        <v>6.0048</v>
       </c>
       <c r="G22" t="n">
-        <v>6.128</v>
+        <v>6.1281</v>
       </c>
       <c r="H22" t="n">
-        <v>6.5944</v>
+        <v>6.6195</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9528</v>
+        <v>6.9724</v>
       </c>
       <c r="J22" t="n">
-        <v>7.312</v>
+        <v>7.3271</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6441</v>
+        <v>7.6552</v>
       </c>
       <c r="L22" t="n">
-        <v>7.9228</v>
+        <v>7.9299</v>
       </c>
       <c r="M22" t="n">
-        <v>8.1214</v>
+        <v>8.1242</v>
       </c>
       <c r="N22" t="n">
-        <v>8.208500000000001</v>
+        <v>8.206799999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>8.1495</v>
+        <v>8.1431</v>
       </c>
       <c r="P22" t="n">
-        <v>7.9102</v>
+        <v>7.8991</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,273 +506,273 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C2" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F2" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J2" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M2" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N2" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P2" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C3" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I3" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L3" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M3" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P3" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C4" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O4" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P4" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G5" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J5" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K5" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M5" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N5" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H6" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L6" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M6" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P6" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q6" t="n">
         <v>6.57</v>
@@ -781,53 +781,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P7" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q7" t="n">
         <v>6.57</v>
@@ -836,713 +836,713 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C8" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M8" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P8" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F9" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J9" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M9" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O9" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G10" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O10" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P10" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H11" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J11" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L11" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K12" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M12" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O12" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P12" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E13" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M13" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L14" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M14" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P14" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C15" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D15" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L15" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M15" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N15" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P15" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M16" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O16" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C17" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D17" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E17" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F17" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M17" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D18" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J18" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I19" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L19" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P19" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.665</v>
+        <v>5.708</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7985</v>
+        <v>5.8363</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8677</v>
+        <v>5.8961</v>
       </c>
       <c r="E20" t="n">
-        <v>6.008</v>
+        <v>6.0051</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1221</v>
+        <v>6.0882</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2584</v>
+        <v>6.2055</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6843</v>
+        <v>6.6782</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9949</v>
+        <v>6.9916</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3144</v>
+        <v>7.3134</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6151</v>
+        <v>7.6158</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8722</v>
+        <v>7.874</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0619</v>
+        <v>8.0641</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1572</v>
+        <v>8.1587</v>
       </c>
       <c r="O20" t="n">
-        <v>8.127700000000001</v>
+        <v>8.1273</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9424</v>
+        <v>7.9386</v>
       </c>
       <c r="Q20" t="n">
         <v>6.47</v>
@@ -1551,111 +1551,111 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.7497</v>
+        <v>5.665</v>
       </c>
       <c r="C21" t="n">
-        <v>5.9028</v>
+        <v>5.7985</v>
       </c>
       <c r="D21" t="n">
-        <v>5.9579</v>
+        <v>5.8677</v>
       </c>
       <c r="E21" t="n">
-        <v>6.0246</v>
+        <v>6.008</v>
       </c>
       <c r="F21" t="n">
-        <v>6.0583</v>
+        <v>6.1221</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1379</v>
+        <v>6.2584</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6607</v>
+        <v>6.6843</v>
       </c>
       <c r="I21" t="n">
-        <v>6.9787</v>
+        <v>6.9949</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3044</v>
+        <v>7.3144</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6104</v>
+        <v>7.6151</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8726</v>
+        <v>7.8722</v>
       </c>
       <c r="M21" t="n">
-        <v>8.0671</v>
+        <v>8.0619</v>
       </c>
       <c r="N21" t="n">
-        <v>8.1668</v>
+        <v>8.1572</v>
       </c>
       <c r="O21" t="n">
-        <v>8.1409</v>
+        <v>8.127700000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.9583</v>
+        <v>7.9424</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.7266</v>
+        <v>5.7497</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7747</v>
+        <v>5.9028</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8124</v>
+        <v>5.9579</v>
       </c>
       <c r="E22" t="n">
-        <v>5.9126</v>
+        <v>6.0246</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0048</v>
+        <v>6.0583</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1281</v>
+        <v>6.1379</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6195</v>
+        <v>6.6607</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9724</v>
+        <v>6.9787</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3271</v>
+        <v>7.3044</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6552</v>
+        <v>7.6104</v>
       </c>
       <c r="L22" t="n">
-        <v>7.9299</v>
+        <v>7.8726</v>
       </c>
       <c r="M22" t="n">
-        <v>8.1242</v>
+        <v>8.0671</v>
       </c>
       <c r="N22" t="n">
-        <v>8.206799999999999</v>
+        <v>8.1668</v>
       </c>
       <c r="O22" t="n">
-        <v>8.1431</v>
+        <v>8.1409</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8991</v>
+        <v>7.9583</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,328 +506,328 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C2" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F2" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I2" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N2" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P2" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C3" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J3" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M3" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N3" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P3" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C4" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L4" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M4" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P4" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C5" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O5" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P5" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G6" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J6" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K6" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M6" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N6" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H7" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L7" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M7" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P7" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q7" t="n">
         <v>6.57</v>
@@ -836,53 +836,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P8" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q8" t="n">
         <v>6.57</v>
@@ -891,771 +891,661 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C9" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M9" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P9" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F10" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J10" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M10" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O10" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F11" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G11" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O11" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P11" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H12" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J12" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L12" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M12" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K13" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M13" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O13" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P13" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E14" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M14" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O14" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L15" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M15" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P15" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C16" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D16" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L16" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M16" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N16" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P16" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H17" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L17" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M17" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O17" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C18" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D18" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E18" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F18" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M18" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J19" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.708</v>
+        <v>5.7963</v>
       </c>
       <c r="C20" t="n">
-        <v>5.8363</v>
+        <v>5.8478</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8961</v>
+        <v>5.8907</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0051</v>
+        <v>6.0077</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0882</v>
+        <v>6.1168</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2055</v>
+        <v>6.2531</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6782</v>
+        <v>6.6882</v>
       </c>
       <c r="I20" t="n">
-        <v>6.9916</v>
+        <v>7.0048</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3134</v>
+        <v>7.329</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6158</v>
+        <v>7.6313</v>
       </c>
       <c r="L20" t="n">
-        <v>7.874</v>
+        <v>7.8848</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0641</v>
+        <v>8.0639</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1587</v>
+        <v>8.1393</v>
       </c>
       <c r="O20" t="n">
-        <v>8.1273</v>
+        <v>8.0791</v>
       </c>
       <c r="P20" t="n">
-        <v>7.9386</v>
+        <v>7.8516</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.47</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5.665</v>
-      </c>
-      <c r="C21" t="n">
-        <v>5.7985</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5.8677</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6.008</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.1221</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.2584</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6.6843</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6.9949</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7.3144</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.6151</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.8722</v>
-      </c>
-      <c r="M21" t="n">
-        <v>8.0619</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8.1572</v>
-      </c>
-      <c r="O21" t="n">
-        <v>8.127700000000001</v>
-      </c>
-      <c r="P21" t="n">
-        <v>7.9424</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.47</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.7497</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.9028</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.9579</v>
-      </c>
-      <c r="E22" t="n">
-        <v>6.0246</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.0583</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.1379</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.6607</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6.9787</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7.3044</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.6104</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.8726</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8.0671</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.1668</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.1409</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.9583</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.48</v>
+        <v>6.49</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,383 +506,383 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K2" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C3" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F3" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I3" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N3" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P3" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C4" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J4" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M4" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N4" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P4" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C5" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I5" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L5" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M5" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P5" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C6" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O6" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P6" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D7" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G7" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J7" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K7" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M7" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N7" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H8" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K8" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L8" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M8" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P8" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q8" t="n">
         <v>6.57</v>
@@ -891,53 +891,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P9" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q9" t="n">
         <v>6.57</v>
@@ -946,605 +946,660 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C10" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M10" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P10" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F11" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J11" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M11" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O11" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G12" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M12" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O12" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P12" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H13" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J13" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L13" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K14" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M14" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N14" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O14" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P14" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E15" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M15" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O15" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L16" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M16" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P16" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C17" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D17" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H17" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L17" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M17" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N17" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P17" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H18" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M18" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O18" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D19" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E19" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F19" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M19" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.7241</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.7793</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.829</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.969</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.2574</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.6879</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.0062</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.3317</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.6331</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.8823</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8.052099999999999</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.112299999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.0299</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7.7731</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>5.7963</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>5.8478</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>5.8907</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>6.0077</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>6.1168</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>6.2531</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>6.6882</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>7.0048</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>7.329</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>7.6313</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>7.8848</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>8.0639</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>8.1393</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>8.0791</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>7.8516</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>6.49</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,438 +506,438 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C2" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K2" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O2" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P2" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K3" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C4" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F4" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I4" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N4" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P4" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C5" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F5" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J5" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M5" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N5" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P5" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C6" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I6" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L6" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M6" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P6" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C7" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O7" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P7" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G8" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J8" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K8" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M8" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N8" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H9" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K9" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L9" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M9" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P9" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q9" t="n">
         <v>6.57</v>
@@ -946,53 +946,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K10" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P10" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q10" t="n">
         <v>6.57</v>
@@ -1001,605 +1001,660 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C11" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M11" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P11" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F12" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J12" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M12" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O12" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F13" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G13" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O13" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P13" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H14" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J14" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L14" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M14" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N14" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O14" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K15" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M15" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N15" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O15" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P15" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E16" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M16" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O16" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H17" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L17" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M17" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P17" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D18" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H18" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L18" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M18" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N18" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P18" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D19" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H19" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M19" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O19" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C20" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D20" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E20" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F20" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M20" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.7241</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.7793</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.829</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.969</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.2574</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.6879</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.0062</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.3317</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.6331</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.8823</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.052099999999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.112299999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.0299</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.7731</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>5.7963</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5.8478</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>5.8907</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>6.0077</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>6.1168</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6.2531</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>6.6882</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>7.0048</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>7.329</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>7.6313</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>7.8848</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>8.0639</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>8.1393</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>8.0791</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>7.8516</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>6.49</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,493 +506,493 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C2" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L2" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P2" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C3" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K3" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O3" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P3" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K4" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C5" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F5" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I5" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N5" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P5" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C6" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D6" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F6" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J6" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M6" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N6" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P6" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C7" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L7" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M7" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P7" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C8" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K8" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O8" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P8" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D9" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G9" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J9" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K9" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M9" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N9" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H10" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L10" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M10" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P10" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q10" t="n">
         <v>6.57</v>
@@ -1001,53 +1001,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K11" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P11" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q11" t="n">
         <v>6.57</v>
@@ -1056,606 +1056,606 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C12" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M12" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P12" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F13" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J13" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M13" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O13" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F14" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G14" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M14" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O14" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P14" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H15" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J15" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L15" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M15" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N15" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O15" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K16" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M16" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N16" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O16" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P16" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E17" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M17" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O17" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H18" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L18" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M18" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P18" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C19" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D19" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H19" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L19" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M19" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N19" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P19" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C20" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D20" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H20" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M20" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O20" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C21" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D21" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E21" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F21" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I21" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M21" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.7963</v>
+        <v>5.7241</v>
       </c>
       <c r="C22" t="n">
-        <v>5.8478</v>
+        <v>5.7793</v>
       </c>
       <c r="D22" t="n">
-        <v>5.8907</v>
+        <v>5.829</v>
       </c>
       <c r="E22" t="n">
-        <v>6.0077</v>
+        <v>5.969</v>
       </c>
       <c r="F22" t="n">
-        <v>6.1168</v>
+        <v>6.101</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2531</v>
+        <v>6.2574</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6882</v>
+        <v>6.6879</v>
       </c>
       <c r="I22" t="n">
-        <v>7.0048</v>
+        <v>7.0062</v>
       </c>
       <c r="J22" t="n">
-        <v>7.329</v>
+        <v>7.3317</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6313</v>
+        <v>7.6331</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8848</v>
+        <v>7.8823</v>
       </c>
       <c r="M22" t="n">
-        <v>8.0639</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.1393</v>
+        <v>8.112299999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>8.0791</v>
+        <v>8.0299</v>
       </c>
       <c r="P22" t="n">
-        <v>7.8516</v>
+        <v>7.7731</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.49</v>
+        <v>6.45</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,548 +506,548 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.142</v>
+        <v>6.0447</v>
       </c>
       <c r="C2" t="n">
-        <v>6.2238</v>
+        <v>6.0921</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2567</v>
+        <v>6.1289</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3069</v>
+        <v>6.2274</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3409</v>
+        <v>6.3192</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3981</v>
+        <v>6.4272</v>
       </c>
       <c r="H2" t="n">
-        <v>6.798</v>
+        <v>6.8006</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1073</v>
+        <v>7.1087</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4281</v>
+        <v>7.4286</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7322</v>
+        <v>7.7318</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9943</v>
+        <v>7.9934</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1904</v>
+        <v>8.1892</v>
       </c>
       <c r="N2" t="n">
-        <v>8.293100000000001</v>
+        <v>8.292</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2713</v>
+        <v>8.270899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0932</v>
+        <v>8.094099999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C3" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L3" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P3" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C4" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K4" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O4" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P4" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K5" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C6" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F6" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I6" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N6" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P6" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C7" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D7" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F7" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J7" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M7" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N7" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P7" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C8" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D8" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K8" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L8" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M8" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P8" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C9" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E9" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K9" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O9" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P9" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D10" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G10" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J10" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K10" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M10" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N10" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H11" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L11" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M11" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P11" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q11" t="n">
         <v>6.57</v>
@@ -1056,53 +1056,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M12" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P12" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q12" t="n">
         <v>6.57</v>
@@ -1111,551 +1111,551 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C13" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M13" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P13" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F14" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J14" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M14" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O14" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F15" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G15" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M15" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O15" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P15" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H16" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J16" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L16" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M16" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N16" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O16" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K17" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M17" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N17" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O17" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P17" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D18" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E18" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M18" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O18" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D19" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H19" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L19" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M19" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P19" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.8118</v>
+        <v>5.7473</v>
       </c>
       <c r="C20" t="n">
-        <v>5.8842</v>
+        <v>5.9212</v>
       </c>
       <c r="D20" t="n">
-        <v>5.929</v>
+        <v>5.9948</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0333</v>
+        <v>6.0982</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1245</v>
+        <v>6.1614</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2504</v>
+        <v>6.2548</v>
       </c>
       <c r="H20" t="n">
-        <v>6.7055</v>
+        <v>6.7065</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0118</v>
+        <v>7.0085</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3282</v>
+        <v>7.3216</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6276</v>
+        <v>7.6208</v>
       </c>
       <c r="L20" t="n">
-        <v>7.886</v>
+        <v>7.884</v>
       </c>
       <c r="M20" t="n">
-        <v>8.080399999999999</v>
+        <v>8.0899</v>
       </c>
       <c r="N20" t="n">
-        <v>8.1846</v>
+        <v>8.214399999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.168900000000001</v>
+        <v>8.2295</v>
       </c>
       <c r="P20" t="n">
-        <v>8.002800000000001</v>
+        <v>8.105499999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.751</v>
+        <v>5.8118</v>
       </c>
       <c r="C21" t="n">
-        <v>5.9207</v>
+        <v>5.8842</v>
       </c>
       <c r="D21" t="n">
-        <v>5.9888</v>
+        <v>5.929</v>
       </c>
       <c r="E21" t="n">
-        <v>6.0904</v>
+        <v>6.0333</v>
       </c>
       <c r="F21" t="n">
-        <v>6.1565</v>
+        <v>6.1245</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2536</v>
+        <v>6.2504</v>
       </c>
       <c r="H21" t="n">
-        <v>6.7091</v>
+        <v>6.7055</v>
       </c>
       <c r="I21" t="n">
-        <v>7.0146</v>
+        <v>7.0118</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3299</v>
+        <v>7.3282</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6251</v>
+        <v>7.6276</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8742</v>
+        <v>7.886</v>
       </c>
       <c r="M21" t="n">
-        <v>8.052099999999999</v>
+        <v>8.080399999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>8.130699999999999</v>
+        <v>8.1846</v>
       </c>
       <c r="O21" t="n">
-        <v>8.079000000000001</v>
+        <v>8.168900000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.8661</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.7241</v>
+        <v>5.751</v>
       </c>
       <c r="C22" t="n">
-        <v>5.7793</v>
+        <v>5.9207</v>
       </c>
       <c r="D22" t="n">
-        <v>5.829</v>
+        <v>5.9888</v>
       </c>
       <c r="E22" t="n">
-        <v>5.969</v>
+        <v>6.0904</v>
       </c>
       <c r="F22" t="n">
-        <v>6.101</v>
+        <v>6.1565</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2574</v>
+        <v>6.2536</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6879</v>
+        <v>6.7091</v>
       </c>
       <c r="I22" t="n">
-        <v>7.0062</v>
+        <v>7.0146</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3317</v>
+        <v>7.3299</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6331</v>
+        <v>7.6251</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8823</v>
+        <v>7.8742</v>
       </c>
       <c r="M22" t="n">
         <v>8.052099999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.112299999999999</v>
+        <v>8.130699999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>8.0299</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>7.7731</v>
+        <v>7.8661</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,603 +506,603 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0447</v>
+        <v>6.0641</v>
       </c>
       <c r="C2" t="n">
-        <v>6.0921</v>
+        <v>6.1274</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1289</v>
+        <v>6.1658</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2274</v>
+        <v>6.255</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3192</v>
+        <v>6.3335</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4272</v>
+        <v>6.425</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8006</v>
+        <v>6.7928</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1087</v>
+        <v>7.1066</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4286</v>
+        <v>7.4313</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7318</v>
+        <v>7.7382</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9934</v>
+        <v>8.001799999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1892</v>
+        <v>8.1975</v>
       </c>
       <c r="N2" t="n">
-        <v>8.292</v>
+        <v>8.2972</v>
       </c>
       <c r="O2" t="n">
-        <v>8.270899999999999</v>
+        <v>8.269500000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>8.094099999999999</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.142</v>
+        <v>6.0447</v>
       </c>
       <c r="C3" t="n">
-        <v>6.2238</v>
+        <v>6.0921</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2567</v>
+        <v>6.1289</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3069</v>
+        <v>6.2274</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3409</v>
+        <v>6.3192</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3981</v>
+        <v>6.4272</v>
       </c>
       <c r="H3" t="n">
-        <v>6.798</v>
+        <v>6.8006</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1073</v>
+        <v>7.1087</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4281</v>
+        <v>7.4286</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7322</v>
+        <v>7.7318</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9943</v>
+        <v>7.9934</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1904</v>
+        <v>8.1892</v>
       </c>
       <c r="N3" t="n">
-        <v>8.293100000000001</v>
+        <v>8.292</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2713</v>
+        <v>8.270899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>8.0932</v>
+        <v>8.094099999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C4" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L4" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P4" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C5" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K5" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O5" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P5" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K6" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C7" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F7" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I7" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N7" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P7" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C8" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D8" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F8" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J8" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K8" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M8" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N8" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P8" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C9" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E9" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I9" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K9" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L9" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M9" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P9" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C10" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O10" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P10" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C11" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D11" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G11" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J11" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K11" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M11" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N11" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H12" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J12" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K12" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L12" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M12" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P12" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q12" t="n">
         <v>6.57</v>
@@ -1111,53 +1111,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P13" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q13" t="n">
         <v>6.57</v>
@@ -1166,496 +1166,386 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C14" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M14" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N14" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P14" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F15" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J15" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M15" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O15" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F16" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G16" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M16" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O16" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P16" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E17" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H17" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J17" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L17" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M17" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N17" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O17" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K18" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M18" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N18" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O18" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P18" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D19" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E19" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M19" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O19" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.7473</v>
+        <v>5.9307</v>
       </c>
       <c r="C20" t="n">
-        <v>5.9212</v>
+        <v>5.9791</v>
       </c>
       <c r="D20" t="n">
-        <v>5.9948</v>
+        <v>6.0113</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0982</v>
+        <v>6.09</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1614</v>
+        <v>6.1607</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2548</v>
+        <v>6.2563</v>
       </c>
       <c r="H20" t="n">
-        <v>6.7065</v>
+        <v>6.6954</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0085</v>
+        <v>7.0298</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3216</v>
+        <v>7.3704</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6208</v>
+        <v>7.6895</v>
       </c>
       <c r="L20" t="n">
-        <v>7.884</v>
+        <v>7.9617</v>
       </c>
       <c r="M20" t="n">
-        <v>8.0899</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>8.214399999999999</v>
+        <v>8.260899999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>8.2295</v>
+        <v>8.2262</v>
       </c>
       <c r="P20" t="n">
-        <v>8.105499999999999</v>
+        <v>8.0245</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.52</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5.8118</v>
-      </c>
-      <c r="C21" t="n">
-        <v>5.8842</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5.929</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6.0333</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.1245</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.2504</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6.7055</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7.0118</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7.3282</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.6276</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.886</v>
-      </c>
-      <c r="M21" t="n">
-        <v>8.080399999999999</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8.1846</v>
-      </c>
-      <c r="O21" t="n">
-        <v>8.168900000000001</v>
-      </c>
-      <c r="P21" t="n">
-        <v>8.002800000000001</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.51</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.751</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.9207</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.9888</v>
-      </c>
-      <c r="E22" t="n">
-        <v>6.0904</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.1565</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.2536</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6.7091</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7.0146</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7.3299</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.6251</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.8742</v>
-      </c>
-      <c r="M22" t="n">
-        <v>8.052099999999999</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.130699999999999</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.079000000000001</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.8661</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.49</v>
+        <v>6.58</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,658 +506,658 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0641</v>
+        <v>6.1097</v>
       </c>
       <c r="C2" t="n">
-        <v>6.1274</v>
+        <v>6.1545</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1658</v>
+        <v>6.1859</v>
       </c>
       <c r="E2" t="n">
-        <v>6.255</v>
+        <v>6.2652</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3335</v>
+        <v>6.338</v>
       </c>
       <c r="G2" t="n">
-        <v>6.425</v>
+        <v>6.4175</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7928</v>
+        <v>6.7924</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1066</v>
+        <v>7.1399</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4313</v>
+        <v>7.4932</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7382</v>
+        <v>7.8199</v>
       </c>
       <c r="L2" t="n">
-        <v>8.001799999999999</v>
+        <v>8.0905</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1975</v>
+        <v>8.2752</v>
       </c>
       <c r="N2" t="n">
-        <v>8.2972</v>
+        <v>8.340199999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>8.269500000000001</v>
+        <v>8.2486</v>
       </c>
       <c r="P2" t="n">
-        <v>8.082000000000001</v>
+        <v>7.9653</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.65</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0447</v>
+        <v>6.0641</v>
       </c>
       <c r="C3" t="n">
-        <v>6.0921</v>
+        <v>6.1274</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1289</v>
+        <v>6.1658</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2274</v>
+        <v>6.255</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3192</v>
+        <v>6.3335</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4272</v>
+        <v>6.425</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8006</v>
+        <v>6.7928</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1087</v>
+        <v>7.1066</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4286</v>
+        <v>7.4313</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7318</v>
+        <v>7.7382</v>
       </c>
       <c r="L3" t="n">
-        <v>7.9934</v>
+        <v>8.001799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1892</v>
+        <v>8.1975</v>
       </c>
       <c r="N3" t="n">
-        <v>8.292</v>
+        <v>8.2972</v>
       </c>
       <c r="O3" t="n">
-        <v>8.270899999999999</v>
+        <v>8.269500000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>8.094099999999999</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.142</v>
+        <v>6.0447</v>
       </c>
       <c r="C4" t="n">
-        <v>6.2238</v>
+        <v>6.0921</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2567</v>
+        <v>6.1289</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3069</v>
+        <v>6.2274</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3409</v>
+        <v>6.3192</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3981</v>
+        <v>6.4272</v>
       </c>
       <c r="H4" t="n">
-        <v>6.798</v>
+        <v>6.8006</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1073</v>
+        <v>7.1087</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4281</v>
+        <v>7.4286</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7322</v>
+        <v>7.7318</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9943</v>
+        <v>7.9934</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1904</v>
+        <v>8.1892</v>
       </c>
       <c r="N4" t="n">
-        <v>8.293100000000001</v>
+        <v>8.292</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2713</v>
+        <v>8.270899999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>8.0932</v>
+        <v>8.094099999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C5" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L5" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P5" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C6" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K6" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O6" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P6" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D7" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K7" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C8" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D8" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F8" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I8" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K8" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N8" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P8" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C9" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E9" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F9" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I9" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J9" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K9" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M9" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N9" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P9" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C10" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D10" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I10" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L10" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M10" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P10" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C11" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O11" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P11" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G12" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K12" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M12" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N12" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H13" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J13" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K13" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L13" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M13" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P13" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q13" t="n">
         <v>6.57</v>
@@ -1166,53 +1166,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M14" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O14" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P14" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q14" t="n">
         <v>6.57</v>
@@ -1221,330 +1221,385 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C15" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M15" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N15" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P15" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F16" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H16" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J16" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M16" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O16" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E17" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F17" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G17" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H17" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M17" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O17" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P17" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D18" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E18" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H18" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J18" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L18" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M18" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N18" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O18" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D19" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K19" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M19" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N19" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O19" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P19" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.9348</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.9757</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.0679</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.1473</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.2521</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.6961</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.0282</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.3671</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.686</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.9605</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8.166499999999999</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.2758</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.256600000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8.076000000000001</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>5.9307</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>5.9791</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>6.0113</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>6.09</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>6.1607</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>6.2563</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>6.6954</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>7.0298</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>7.3704</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>7.6895</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>7.9617</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>8.161799999999999</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>8.260899999999999</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>8.2262</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>8.0245</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>6.58</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,713 +506,713 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1097</v>
+        <v>5.9669</v>
       </c>
       <c r="C2" t="n">
-        <v>6.1545</v>
+        <v>6.0199</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1859</v>
+        <v>6.0643</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2652</v>
+        <v>6.1865</v>
       </c>
       <c r="F2" t="n">
-        <v>6.338</v>
+        <v>6.3014</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4175</v>
+        <v>6.4379</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7924</v>
+        <v>6.8462</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1399</v>
+        <v>7.1634</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4932</v>
+        <v>7.4916</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8199</v>
+        <v>7.7998</v>
       </c>
       <c r="L2" t="n">
-        <v>8.0905</v>
+        <v>8.0603</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2752</v>
+        <v>8.2462</v>
       </c>
       <c r="N2" t="n">
-        <v>8.340199999999999</v>
+        <v>8.327400000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2486</v>
+        <v>8.270300000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9653</v>
+        <v>8.041600000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.69</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0641</v>
+        <v>6.1097</v>
       </c>
       <c r="C3" t="n">
-        <v>6.1274</v>
+        <v>6.1545</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1658</v>
+        <v>6.1859</v>
       </c>
       <c r="E3" t="n">
-        <v>6.255</v>
+        <v>6.2652</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3335</v>
+        <v>6.338</v>
       </c>
       <c r="G3" t="n">
-        <v>6.425</v>
+        <v>6.4175</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7928</v>
+        <v>6.7924</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1066</v>
+        <v>7.1399</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4313</v>
+        <v>7.4932</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7382</v>
+        <v>7.8199</v>
       </c>
       <c r="L3" t="n">
-        <v>8.001799999999999</v>
+        <v>8.0905</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1975</v>
+        <v>8.2752</v>
       </c>
       <c r="N3" t="n">
-        <v>8.2972</v>
+        <v>8.340199999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>8.269500000000001</v>
+        <v>8.2486</v>
       </c>
       <c r="P3" t="n">
-        <v>8.082000000000001</v>
+        <v>7.9653</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.65</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0447</v>
+        <v>6.0641</v>
       </c>
       <c r="C4" t="n">
-        <v>6.0921</v>
+        <v>6.1274</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1289</v>
+        <v>6.1658</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2274</v>
+        <v>6.255</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3192</v>
+        <v>6.3335</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4272</v>
+        <v>6.425</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8006</v>
+        <v>6.7928</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1087</v>
+        <v>7.1066</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4286</v>
+        <v>7.4313</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7318</v>
+        <v>7.7382</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9934</v>
+        <v>8.001799999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1892</v>
+        <v>8.1975</v>
       </c>
       <c r="N4" t="n">
-        <v>8.292</v>
+        <v>8.2972</v>
       </c>
       <c r="O4" t="n">
-        <v>8.270899999999999</v>
+        <v>8.269500000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>8.094099999999999</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.142</v>
+        <v>6.0447</v>
       </c>
       <c r="C5" t="n">
-        <v>6.2238</v>
+        <v>6.0921</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2567</v>
+        <v>6.1289</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3069</v>
+        <v>6.2274</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3409</v>
+        <v>6.3192</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3981</v>
+        <v>6.4272</v>
       </c>
       <c r="H5" t="n">
-        <v>6.798</v>
+        <v>6.8006</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1073</v>
+        <v>7.1087</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4281</v>
+        <v>7.4286</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7322</v>
+        <v>7.7318</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9943</v>
+        <v>7.9934</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1904</v>
+        <v>8.1892</v>
       </c>
       <c r="N5" t="n">
-        <v>8.293100000000001</v>
+        <v>8.292</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2713</v>
+        <v>8.270899999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>8.0932</v>
+        <v>8.094099999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C6" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L6" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N6" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P6" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C7" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K7" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O7" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P7" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C8" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D8" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K8" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C9" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E9" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F9" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I9" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K9" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N9" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P9" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C10" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D10" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E10" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J10" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M10" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N10" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P10" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C11" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D11" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I11" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L11" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M11" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P11" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C12" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J12" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K12" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O12" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P12" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G13" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K13" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M13" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N13" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H14" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J14" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K14" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L14" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M14" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O14" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P14" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q14" t="n">
         <v>6.57</v>
@@ -1221,53 +1221,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M15" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O15" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P15" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q15" t="n">
         <v>6.57</v>
@@ -1276,330 +1276,385 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C16" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M16" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N16" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P16" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F17" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J17" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M17" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O17" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D18" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E18" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F18" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G18" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H18" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M18" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O18" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P18" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D19" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E19" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H19" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J19" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L19" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M19" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N19" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O19" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C20" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D20" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K20" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M20" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N20" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O20" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P20" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.9348</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.9757</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.0679</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.1473</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.2521</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.6961</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.0282</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.3671</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.686</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.9605</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.166499999999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.2758</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8.256600000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8.076000000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>5.9307</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>5.9791</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>6.0113</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>6.09</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>6.1607</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6.2563</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>6.6954</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>7.0298</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>7.3704</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>7.6895</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>7.9617</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>8.161799999999999</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>8.260899999999999</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>8.2262</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>8.0245</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>6.58</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,768 +506,768 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9669</v>
+        <v>6.1181</v>
       </c>
       <c r="C2" t="n">
-        <v>6.0199</v>
+        <v>6.2886</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0643</v>
+        <v>6.3505</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1865</v>
+        <v>6.4282</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3014</v>
+        <v>6.4707</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4379</v>
+        <v>6.5176</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8462</v>
+        <v>6.8605</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1634</v>
+        <v>7.1709</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4916</v>
+        <v>7.4936</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7998</v>
+        <v>7.7975</v>
       </c>
       <c r="L2" t="n">
-        <v>8.0603</v>
+        <v>8.055099999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2462</v>
+        <v>8.2401</v>
       </c>
       <c r="N2" t="n">
-        <v>8.327400000000001</v>
+        <v>8.322900000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>8.270300000000001</v>
+        <v>8.2705</v>
       </c>
       <c r="P2" t="n">
-        <v>8.041600000000001</v>
+        <v>8.0502</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.66</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1097</v>
+        <v>5.9669</v>
       </c>
       <c r="C3" t="n">
-        <v>6.1545</v>
+        <v>6.0199</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1859</v>
+        <v>6.0643</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2652</v>
+        <v>6.1865</v>
       </c>
       <c r="F3" t="n">
-        <v>6.338</v>
+        <v>6.3014</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4175</v>
+        <v>6.4379</v>
       </c>
       <c r="H3" t="n">
-        <v>6.7924</v>
+        <v>6.8462</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1399</v>
+        <v>7.1634</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4932</v>
+        <v>7.4916</v>
       </c>
       <c r="K3" t="n">
-        <v>7.8199</v>
+        <v>7.7998</v>
       </c>
       <c r="L3" t="n">
-        <v>8.0905</v>
+        <v>8.0603</v>
       </c>
       <c r="M3" t="n">
-        <v>8.2752</v>
+        <v>8.2462</v>
       </c>
       <c r="N3" t="n">
-        <v>8.340199999999999</v>
+        <v>8.327400000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8.2486</v>
+        <v>8.270300000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>7.9653</v>
+        <v>8.041600000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.69</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0641</v>
+        <v>6.1097</v>
       </c>
       <c r="C4" t="n">
-        <v>6.1274</v>
+        <v>6.1545</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1658</v>
+        <v>6.1859</v>
       </c>
       <c r="E4" t="n">
-        <v>6.255</v>
+        <v>6.2652</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3335</v>
+        <v>6.338</v>
       </c>
       <c r="G4" t="n">
-        <v>6.425</v>
+        <v>6.4175</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7928</v>
+        <v>6.7924</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1066</v>
+        <v>7.1399</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4313</v>
+        <v>7.4932</v>
       </c>
       <c r="K4" t="n">
-        <v>7.7382</v>
+        <v>7.8199</v>
       </c>
       <c r="L4" t="n">
-        <v>8.001799999999999</v>
+        <v>8.0905</v>
       </c>
       <c r="M4" t="n">
-        <v>8.1975</v>
+        <v>8.2752</v>
       </c>
       <c r="N4" t="n">
-        <v>8.2972</v>
+        <v>8.340199999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>8.269500000000001</v>
+        <v>8.2486</v>
       </c>
       <c r="P4" t="n">
-        <v>8.082000000000001</v>
+        <v>7.9653</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.65</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0447</v>
+        <v>6.0641</v>
       </c>
       <c r="C5" t="n">
-        <v>6.0921</v>
+        <v>6.1274</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1289</v>
+        <v>6.1658</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2274</v>
+        <v>6.255</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3192</v>
+        <v>6.3335</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4272</v>
+        <v>6.425</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8006</v>
+        <v>6.7928</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1087</v>
+        <v>7.1066</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4286</v>
+        <v>7.4313</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7318</v>
+        <v>7.7382</v>
       </c>
       <c r="L5" t="n">
-        <v>7.9934</v>
+        <v>8.001799999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1892</v>
+        <v>8.1975</v>
       </c>
       <c r="N5" t="n">
-        <v>8.292</v>
+        <v>8.2972</v>
       </c>
       <c r="O5" t="n">
-        <v>8.270899999999999</v>
+        <v>8.269500000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>8.094099999999999</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.142</v>
+        <v>6.0447</v>
       </c>
       <c r="C6" t="n">
-        <v>6.2238</v>
+        <v>6.0921</v>
       </c>
       <c r="D6" t="n">
-        <v>6.2567</v>
+        <v>6.1289</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3069</v>
+        <v>6.2274</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3409</v>
+        <v>6.3192</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3981</v>
+        <v>6.4272</v>
       </c>
       <c r="H6" t="n">
-        <v>6.798</v>
+        <v>6.8006</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1073</v>
+        <v>7.1087</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4281</v>
+        <v>7.4286</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7322</v>
+        <v>7.7318</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9943</v>
+        <v>7.9934</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1904</v>
+        <v>8.1892</v>
       </c>
       <c r="N6" t="n">
-        <v>8.293100000000001</v>
+        <v>8.292</v>
       </c>
       <c r="O6" t="n">
-        <v>8.2713</v>
+        <v>8.270899999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>8.0932</v>
+        <v>8.094099999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C7" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L7" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N7" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P7" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C8" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D8" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K8" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O8" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P8" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E9" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I9" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K9" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O9" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C10" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D10" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E10" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F10" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I10" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N10" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P10" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C11" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D11" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E11" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F11" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G11" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I11" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J11" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M11" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N11" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P11" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C12" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I12" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J12" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K12" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L12" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M12" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P12" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C13" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J13" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K13" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O13" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P13" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C14" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G14" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K14" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M14" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N14" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O14" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H15" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J15" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K15" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L15" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M15" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O15" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P15" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q15" t="n">
         <v>6.57</v>
@@ -1276,53 +1276,53 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J16" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L16" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M16" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O16" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P16" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q16" t="n">
         <v>6.57</v>
@@ -1331,331 +1331,331 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C17" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H17" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M17" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N17" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P17" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C18" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D18" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F18" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J18" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M18" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O18" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D19" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E19" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F19" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G19" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H19" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J19" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M19" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O19" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P19" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C20" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D20" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E20" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H20" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J20" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L20" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M20" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N20" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O20" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C21" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D21" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E21" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F21" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I21" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J21" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K21" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L21" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M21" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N21" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O21" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P21" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.9307</v>
+        <v>5.865</v>
       </c>
       <c r="C22" t="n">
-        <v>5.9791</v>
+        <v>5.9348</v>
       </c>
       <c r="D22" t="n">
-        <v>6.0113</v>
+        <v>5.9757</v>
       </c>
       <c r="E22" t="n">
-        <v>6.09</v>
+        <v>6.0679</v>
       </c>
       <c r="F22" t="n">
-        <v>6.1607</v>
+        <v>6.1473</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2563</v>
+        <v>6.2521</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6954</v>
+        <v>6.6961</v>
       </c>
       <c r="I22" t="n">
-        <v>7.0298</v>
+        <v>7.0282</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3704</v>
+        <v>7.3671</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6895</v>
+        <v>7.686</v>
       </c>
       <c r="L22" t="n">
-        <v>7.9617</v>
+        <v>7.9605</v>
       </c>
       <c r="M22" t="n">
-        <v>8.161799999999999</v>
+        <v>8.166499999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.260899999999999</v>
+        <v>8.2758</v>
       </c>
       <c r="O22" t="n">
-        <v>8.2262</v>
+        <v>8.256600000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>8.0245</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_temp.xlsx
@@ -506,823 +506,823 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1181</v>
+        <v>6.0216</v>
       </c>
       <c r="C2" t="n">
-        <v>6.2886</v>
+        <v>6.1763</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3505</v>
+        <v>6.2498</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4282</v>
+        <v>6.3875</v>
       </c>
       <c r="F2" t="n">
-        <v>6.4707</v>
+        <v>6.4957</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5176</v>
+        <v>6.5903</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8605</v>
+        <v>6.8624</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1709</v>
+        <v>7.169</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4936</v>
+        <v>7.4888</v>
       </c>
       <c r="K2" t="n">
-        <v>7.7975</v>
+        <v>7.792</v>
       </c>
       <c r="L2" t="n">
-        <v>8.055099999999999</v>
+        <v>8.0528</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2401</v>
+        <v>8.2461</v>
       </c>
       <c r="N2" t="n">
-        <v>8.322900000000001</v>
+        <v>8.3438</v>
       </c>
       <c r="O2" t="n">
-        <v>8.2705</v>
+        <v>8.314299999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>8.0502</v>
+        <v>8.1251</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.76</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9669</v>
+        <v>6.1181</v>
       </c>
       <c r="C3" t="n">
-        <v>6.0199</v>
+        <v>6.2886</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0643</v>
+        <v>6.3505</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1865</v>
+        <v>6.4282</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3014</v>
+        <v>6.4707</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4379</v>
+        <v>6.5176</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8462</v>
+        <v>6.8605</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1634</v>
+        <v>7.1709</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4916</v>
+        <v>7.4936</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7998</v>
+        <v>7.7975</v>
       </c>
       <c r="L3" t="n">
-        <v>8.0603</v>
+        <v>8.055099999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>8.2462</v>
+        <v>8.2401</v>
       </c>
       <c r="N3" t="n">
-        <v>8.327400000000001</v>
+        <v>8.322900000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8.270300000000001</v>
+        <v>8.2705</v>
       </c>
       <c r="P3" t="n">
-        <v>8.041600000000001</v>
+        <v>8.0502</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.66</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1097</v>
+        <v>5.9669</v>
       </c>
       <c r="C4" t="n">
-        <v>6.1545</v>
+        <v>6.0199</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1859</v>
+        <v>6.0643</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2652</v>
+        <v>6.1865</v>
       </c>
       <c r="F4" t="n">
-        <v>6.338</v>
+        <v>6.3014</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4175</v>
+        <v>6.4379</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7924</v>
+        <v>6.8462</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1399</v>
+        <v>7.1634</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4932</v>
+        <v>7.4916</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8199</v>
+        <v>7.7998</v>
       </c>
       <c r="L4" t="n">
-        <v>8.0905</v>
+        <v>8.0603</v>
       </c>
       <c r="M4" t="n">
-        <v>8.2752</v>
+        <v>8.2462</v>
       </c>
       <c r="N4" t="n">
-        <v>8.340199999999999</v>
+        <v>8.327400000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>8.2486</v>
+        <v>8.270300000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>7.9653</v>
+        <v>8.041600000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.69</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0641</v>
+        <v>6.1097</v>
       </c>
       <c r="C5" t="n">
-        <v>6.1274</v>
+        <v>6.1545</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1658</v>
+        <v>6.1859</v>
       </c>
       <c r="E5" t="n">
-        <v>6.255</v>
+        <v>6.2652</v>
       </c>
       <c r="F5" t="n">
-        <v>6.3335</v>
+        <v>6.338</v>
       </c>
       <c r="G5" t="n">
-        <v>6.425</v>
+        <v>6.4175</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7928</v>
+        <v>6.7924</v>
       </c>
       <c r="I5" t="n">
-        <v>7.1066</v>
+        <v>7.1399</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4313</v>
+        <v>7.4932</v>
       </c>
       <c r="K5" t="n">
-        <v>7.7382</v>
+        <v>7.8199</v>
       </c>
       <c r="L5" t="n">
-        <v>8.001799999999999</v>
+        <v>8.0905</v>
       </c>
       <c r="M5" t="n">
-        <v>8.1975</v>
+        <v>8.2752</v>
       </c>
       <c r="N5" t="n">
-        <v>8.2972</v>
+        <v>8.340199999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.269500000000001</v>
+        <v>8.2486</v>
       </c>
       <c r="P5" t="n">
-        <v>8.082000000000001</v>
+        <v>7.9653</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.65</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0447</v>
+        <v>6.0641</v>
       </c>
       <c r="C6" t="n">
-        <v>6.0921</v>
+        <v>6.1274</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1289</v>
+        <v>6.1658</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2274</v>
+        <v>6.255</v>
       </c>
       <c r="F6" t="n">
-        <v>6.3192</v>
+        <v>6.3335</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4272</v>
+        <v>6.425</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8006</v>
+        <v>6.7928</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1087</v>
+        <v>7.1066</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4286</v>
+        <v>7.4313</v>
       </c>
       <c r="K6" t="n">
-        <v>7.7318</v>
+        <v>7.7382</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9934</v>
+        <v>8.001799999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>8.1892</v>
+        <v>8.1975</v>
       </c>
       <c r="N6" t="n">
-        <v>8.292</v>
+        <v>8.2972</v>
       </c>
       <c r="O6" t="n">
-        <v>8.270899999999999</v>
+        <v>8.269500000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>8.094099999999999</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.142</v>
+        <v>6.0447</v>
       </c>
       <c r="C7" t="n">
-        <v>6.2238</v>
+        <v>6.0921</v>
       </c>
       <c r="D7" t="n">
-        <v>6.2567</v>
+        <v>6.1289</v>
       </c>
       <c r="E7" t="n">
-        <v>6.3069</v>
+        <v>6.2274</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3409</v>
+        <v>6.3192</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3981</v>
+        <v>6.4272</v>
       </c>
       <c r="H7" t="n">
-        <v>6.798</v>
+        <v>6.8006</v>
       </c>
       <c r="I7" t="n">
-        <v>7.1073</v>
+        <v>7.1087</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4281</v>
+        <v>7.4286</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7322</v>
+        <v>7.7318</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9943</v>
+        <v>7.9934</v>
       </c>
       <c r="M7" t="n">
-        <v>8.1904</v>
+        <v>8.1892</v>
       </c>
       <c r="N7" t="n">
-        <v>8.293100000000001</v>
+        <v>8.292</v>
       </c>
       <c r="O7" t="n">
-        <v>8.2713</v>
+        <v>8.270899999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>8.0932</v>
+        <v>8.094099999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.0525</v>
+        <v>6.142</v>
       </c>
       <c r="C8" t="n">
-        <v>6.1199</v>
+        <v>6.2238</v>
       </c>
       <c r="D8" t="n">
-        <v>6.1621</v>
+        <v>6.2567</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2623</v>
+        <v>6.3069</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3513</v>
+        <v>6.3409</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4506</v>
+        <v>6.3981</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8022</v>
+        <v>6.798</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1095</v>
+        <v>7.1073</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4288</v>
+        <v>7.4281</v>
       </c>
       <c r="K8" t="n">
-        <v>7.7316</v>
+        <v>7.7322</v>
       </c>
       <c r="L8" t="n">
-        <v>7.993</v>
+        <v>7.9943</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1889</v>
+        <v>8.1904</v>
       </c>
       <c r="N8" t="n">
-        <v>8.2921</v>
+        <v>8.293100000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>8.2719</v>
+        <v>8.2713</v>
       </c>
       <c r="P8" t="n">
-        <v>8.096399999999999</v>
+        <v>8.0932</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.1006</v>
+        <v>6.0525</v>
       </c>
       <c r="C9" t="n">
-        <v>6.1486</v>
+        <v>6.1199</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1848</v>
+        <v>6.1621</v>
       </c>
       <c r="E9" t="n">
-        <v>6.2801</v>
+        <v>6.2623</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3688</v>
+        <v>6.3513</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4664</v>
+        <v>6.4506</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8059</v>
+        <v>6.8022</v>
       </c>
       <c r="I9" t="n">
-        <v>7.1115</v>
+        <v>7.1095</v>
       </c>
       <c r="J9" t="n">
-        <v>7.4293</v>
+        <v>7.4288</v>
       </c>
       <c r="K9" t="n">
-        <v>7.731</v>
+        <v>7.7316</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9917</v>
+        <v>7.993</v>
       </c>
       <c r="M9" t="n">
-        <v>8.1874</v>
+        <v>8.1889</v>
       </c>
       <c r="N9" t="n">
-        <v>8.2913</v>
+        <v>8.2921</v>
       </c>
       <c r="O9" t="n">
-        <v>8.272500000000001</v>
+        <v>8.2719</v>
       </c>
       <c r="P9" t="n">
-        <v>8.099500000000001</v>
+        <v>8.096399999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.9191</v>
+        <v>6.1006</v>
       </c>
       <c r="C10" t="n">
-        <v>5.9848</v>
+        <v>6.1486</v>
       </c>
       <c r="D10" t="n">
-        <v>6.0408</v>
+        <v>6.1848</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1957</v>
+        <v>6.2801</v>
       </c>
       <c r="F10" t="n">
-        <v>6.3416</v>
+        <v>6.3688</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4839</v>
+        <v>6.4664</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7908</v>
+        <v>6.8059</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1004</v>
+        <v>7.1115</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4215</v>
+        <v>7.4293</v>
       </c>
       <c r="K10" t="n">
-        <v>7.726</v>
+        <v>7.731</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9893</v>
+        <v>7.9917</v>
       </c>
       <c r="M10" t="n">
-        <v>8.1875</v>
+        <v>8.1874</v>
       </c>
       <c r="N10" t="n">
-        <v>8.2935</v>
+        <v>8.2913</v>
       </c>
       <c r="O10" t="n">
-        <v>8.2765</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>8.104699999999999</v>
+        <v>8.099500000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.62</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.0726</v>
+        <v>5.9191</v>
       </c>
       <c r="C11" t="n">
-        <v>6.111</v>
+        <v>5.9848</v>
       </c>
       <c r="D11" t="n">
-        <v>6.1378</v>
+        <v>6.0408</v>
       </c>
       <c r="E11" t="n">
-        <v>6.2058</v>
+        <v>6.1957</v>
       </c>
       <c r="F11" t="n">
-        <v>6.268</v>
+        <v>6.3416</v>
       </c>
       <c r="G11" t="n">
-        <v>6.3566</v>
+        <v>6.4839</v>
       </c>
       <c r="H11" t="n">
-        <v>6.7752</v>
+        <v>6.7908</v>
       </c>
       <c r="I11" t="n">
-        <v>7.092</v>
+        <v>7.1004</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4189</v>
+        <v>7.4215</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7281</v>
+        <v>7.726</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9944</v>
+        <v>7.9893</v>
       </c>
       <c r="M11" t="n">
-        <v>8.1937</v>
+        <v>8.1875</v>
       </c>
       <c r="N11" t="n">
-        <v>8.298299999999999</v>
+        <v>8.2935</v>
       </c>
       <c r="O11" t="n">
-        <v>8.2766</v>
+        <v>8.2765</v>
       </c>
       <c r="P11" t="n">
-        <v>8.096299999999999</v>
+        <v>8.104699999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.0374</v>
+        <v>6.0726</v>
       </c>
       <c r="C12" t="n">
-        <v>6.164</v>
+        <v>6.111</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2043</v>
+        <v>6.1378</v>
       </c>
       <c r="E12" t="n">
-        <v>6.2399</v>
+        <v>6.2058</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2483</v>
+        <v>6.268</v>
       </c>
       <c r="G12" t="n">
-        <v>6.3025</v>
+        <v>6.3566</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7991</v>
+        <v>6.7752</v>
       </c>
       <c r="I12" t="n">
-        <v>7.1076</v>
+        <v>7.092</v>
       </c>
       <c r="J12" t="n">
-        <v>7.428</v>
+        <v>7.4189</v>
       </c>
       <c r="K12" t="n">
-        <v>7.7321</v>
+        <v>7.7281</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9953</v>
+        <v>7.9944</v>
       </c>
       <c r="M12" t="n">
-        <v>8.193899999999999</v>
+        <v>8.1937</v>
       </c>
       <c r="N12" t="n">
-        <v>8.300700000000001</v>
+        <v>8.298299999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>8.2851</v>
+        <v>8.2766</v>
       </c>
       <c r="P12" t="n">
-        <v>8.1153</v>
+        <v>8.096299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.0361</v>
+        <v>6.0374</v>
       </c>
       <c r="C13" t="n">
-        <v>6.0814</v>
+        <v>6.164</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1027</v>
+        <v>6.2043</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1425</v>
+        <v>6.2399</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1739</v>
+        <v>6.2483</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2526</v>
+        <v>6.3025</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7645</v>
+        <v>6.7991</v>
       </c>
       <c r="I13" t="n">
-        <v>7.0908</v>
+        <v>7.1076</v>
       </c>
       <c r="J13" t="n">
-        <v>7.4256</v>
+        <v>7.428</v>
       </c>
       <c r="K13" t="n">
-        <v>7.7398</v>
+        <v>7.7321</v>
       </c>
       <c r="L13" t="n">
-        <v>8.007300000000001</v>
+        <v>7.9953</v>
       </c>
       <c r="M13" t="n">
-        <v>8.2021</v>
+        <v>8.193899999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>8.2951</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>8.2531</v>
+        <v>8.2851</v>
       </c>
       <c r="P13" t="n">
-        <v>8.042899999999999</v>
+        <v>8.1153</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8504</v>
+        <v>6.0361</v>
       </c>
       <c r="C14" t="n">
-        <v>6.0013</v>
+        <v>6.0814</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0539</v>
+        <v>6.1027</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1134</v>
+        <v>6.1425</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1404</v>
+        <v>6.1739</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2085</v>
+        <v>6.2526</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7266</v>
+        <v>6.7645</v>
       </c>
       <c r="I14" t="n">
-        <v>7.0616</v>
+        <v>7.0908</v>
       </c>
       <c r="J14" t="n">
-        <v>7.4033</v>
+        <v>7.4256</v>
       </c>
       <c r="K14" t="n">
-        <v>7.7238</v>
+        <v>7.7398</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9975</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>8.1989</v>
+        <v>8.2021</v>
       </c>
       <c r="N14" t="n">
-        <v>8.2988</v>
+        <v>8.2951</v>
       </c>
       <c r="O14" t="n">
-        <v>8.264099999999999</v>
+        <v>8.2531</v>
       </c>
       <c r="P14" t="n">
-        <v>8.0611</v>
+        <v>8.042899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.8565</v>
+        <v>5.8504</v>
       </c>
       <c r="C15" t="n">
-        <v>5.9197</v>
+        <v>6.0013</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9563</v>
+        <v>6.0539</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0376</v>
+        <v>6.1134</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1073</v>
+        <v>6.1404</v>
       </c>
       <c r="G15" t="n">
-        <v>6.216</v>
+        <v>6.2085</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7171</v>
+        <v>6.7266</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0535</v>
+        <v>7.0616</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3966</v>
+        <v>7.4033</v>
       </c>
       <c r="K15" t="n">
-        <v>7.719</v>
+        <v>7.7238</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9961</v>
+        <v>7.9975</v>
       </c>
       <c r="M15" t="n">
-        <v>8.202999999999999</v>
+        <v>8.1989</v>
       </c>
       <c r="N15" t="n">
-        <v>8.3109</v>
+        <v>8.2988</v>
       </c>
       <c r="O15" t="n">
-        <v>8.2872</v>
+        <v>8.264099999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>8.0983</v>
+        <v>8.0611</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8032</v>
+        <v>5.8565</v>
       </c>
       <c r="C16" t="n">
-        <v>5.9452</v>
+        <v>5.9197</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0002</v>
+        <v>5.9563</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0777</v>
+        <v>6.0376</v>
       </c>
       <c r="F16" t="n">
-        <v>6.1253</v>
+        <v>6.1073</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2111</v>
+        <v>6.216</v>
       </c>
       <c r="H16" t="n">
-        <v>6.721</v>
+        <v>6.7171</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0575</v>
+        <v>7.0535</v>
       </c>
       <c r="J16" t="n">
-        <v>7.4007</v>
+        <v>7.3966</v>
       </c>
       <c r="K16" t="n">
-        <v>7.7232</v>
+        <v>7.719</v>
       </c>
       <c r="L16" t="n">
-        <v>8.0001</v>
+        <v>7.9961</v>
       </c>
       <c r="M16" t="n">
-        <v>8.206300000000001</v>
+        <v>8.202999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.3131</v>
+        <v>8.3109</v>
       </c>
       <c r="O16" t="n">
-        <v>8.2875</v>
+        <v>8.2872</v>
       </c>
       <c r="P16" t="n">
-        <v>8.0961</v>
+        <v>8.0983</v>
       </c>
       <c r="Q16" t="n">
         <v>6.57</v>
@@ -1331,53 +1331,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.8051</v>
+        <v>5.8032</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9039</v>
+        <v>5.9452</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9509</v>
+        <v>6.0002</v>
       </c>
       <c r="E17" t="n">
-        <v>6.0391</v>
+        <v>6.0777</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1075</v>
+        <v>6.1253</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2204</v>
+        <v>6.2111</v>
       </c>
       <c r="H17" t="n">
-        <v>6.7299</v>
+        <v>6.721</v>
       </c>
       <c r="I17" t="n">
-        <v>7.0481</v>
+        <v>7.0575</v>
       </c>
       <c r="J17" t="n">
-        <v>7.3758</v>
+        <v>7.4007</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6871</v>
+        <v>7.7232</v>
       </c>
       <c r="L17" t="n">
-        <v>7.9588</v>
+        <v>8.0001</v>
       </c>
       <c r="M17" t="n">
-        <v>8.1683</v>
+        <v>8.206300000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>8.289300000000001</v>
+        <v>8.3131</v>
       </c>
       <c r="O17" t="n">
-        <v>8.2918</v>
+        <v>8.2875</v>
       </c>
       <c r="P17" t="n">
-        <v>8.144</v>
+        <v>8.0961</v>
       </c>
       <c r="Q17" t="n">
         <v>6.57</v>
@@ -1386,276 +1386,276 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.862</v>
+        <v>5.8051</v>
       </c>
       <c r="C18" t="n">
-        <v>5.96</v>
+        <v>5.9039</v>
       </c>
       <c r="D18" t="n">
-        <v>6.0021</v>
+        <v>5.9509</v>
       </c>
       <c r="E18" t="n">
-        <v>6.0719</v>
+        <v>6.0391</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1217</v>
+        <v>6.1075</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2208</v>
+        <v>6.2204</v>
       </c>
       <c r="H18" t="n">
-        <v>6.7446</v>
+        <v>6.7299</v>
       </c>
       <c r="I18" t="n">
-        <v>7.0616</v>
+        <v>7.0481</v>
       </c>
       <c r="J18" t="n">
-        <v>7.3885</v>
+        <v>7.3758</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6987</v>
+        <v>7.6871</v>
       </c>
       <c r="L18" t="n">
-        <v>7.9685</v>
+        <v>7.9588</v>
       </c>
       <c r="M18" t="n">
-        <v>8.174799999999999</v>
+        <v>8.1683</v>
       </c>
       <c r="N18" t="n">
-        <v>8.2911</v>
+        <v>8.289300000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>8.286899999999999</v>
+        <v>8.2918</v>
       </c>
       <c r="P18" t="n">
-        <v>8.1303</v>
+        <v>8.144</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.7798</v>
+        <v>5.862</v>
       </c>
       <c r="C19" t="n">
-        <v>5.9175</v>
+        <v>5.96</v>
       </c>
       <c r="D19" t="n">
-        <v>5.9813</v>
+        <v>6.0021</v>
       </c>
       <c r="E19" t="n">
-        <v>6.0969</v>
+        <v>6.0719</v>
       </c>
       <c r="F19" t="n">
-        <v>6.185</v>
+        <v>6.1217</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2795</v>
+        <v>6.2208</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6715</v>
+        <v>6.7446</v>
       </c>
       <c r="I19" t="n">
-        <v>7.0111</v>
+        <v>7.0616</v>
       </c>
       <c r="J19" t="n">
-        <v>7.356</v>
+        <v>7.3885</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6798</v>
+        <v>7.6987</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9585</v>
+        <v>7.9685</v>
       </c>
       <c r="M19" t="n">
-        <v>8.167400000000001</v>
+        <v>8.174799999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>8.2784</v>
+        <v>8.2911</v>
       </c>
       <c r="O19" t="n">
-        <v>8.259</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>8.076000000000001</v>
+        <v>8.1303</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.8491</v>
+        <v>5.7798</v>
       </c>
       <c r="C20" t="n">
-        <v>5.9562</v>
+        <v>5.9175</v>
       </c>
       <c r="D20" t="n">
-        <v>6.0181</v>
+        <v>5.9813</v>
       </c>
       <c r="E20" t="n">
-        <v>6.1564</v>
+        <v>6.0969</v>
       </c>
       <c r="F20" t="n">
-        <v>6.2752</v>
+        <v>6.185</v>
       </c>
       <c r="G20" t="n">
-        <v>6.387</v>
+        <v>6.2795</v>
       </c>
       <c r="H20" t="n">
-        <v>6.7072</v>
+        <v>6.6715</v>
       </c>
       <c r="I20" t="n">
-        <v>7.0342</v>
+        <v>7.0111</v>
       </c>
       <c r="J20" t="n">
-        <v>7.3689</v>
+        <v>7.356</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6844</v>
+        <v>7.6798</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9567</v>
+        <v>7.9585</v>
       </c>
       <c r="M20" t="n">
-        <v>8.1617</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>8.2719</v>
+        <v>8.2784</v>
       </c>
       <c r="O20" t="n">
-        <v>8.255699999999999</v>
+        <v>8.259</v>
       </c>
       <c r="P20" t="n">
-        <v>8.0808</v>
+        <v>8.076000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.8794</v>
+        <v>5.8491</v>
       </c>
       <c r="C21" t="n">
-        <v>5.9956</v>
+        <v>5.9562</v>
       </c>
       <c r="D21" t="n">
-        <v>6.0401</v>
+        <v>6.0181</v>
       </c>
       <c r="E21" t="n">
-        <v>6.1013</v>
+        <v>6.1564</v>
       </c>
       <c r="F21" t="n">
-        <v>6.1381</v>
+        <v>6.2752</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2096</v>
+        <v>6.387</v>
       </c>
       <c r="H21" t="n">
-        <v>6.695</v>
+        <v>6.7072</v>
       </c>
       <c r="I21" t="n">
-        <v>7.0277</v>
+        <v>7.0342</v>
       </c>
       <c r="J21" t="n">
-        <v>7.367</v>
+        <v>7.3689</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6862</v>
+        <v>7.6844</v>
       </c>
       <c r="L21" t="n">
-        <v>7.961</v>
+        <v>7.9567</v>
       </c>
       <c r="M21" t="n">
-        <v>8.1669</v>
+        <v>8.1617</v>
       </c>
       <c r="N21" t="n">
-        <v>8.2759</v>
+        <v>8.2719</v>
       </c>
       <c r="O21" t="n">
-        <v>8.2561</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>8.074400000000001</v>
+        <v>8.0808</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.865</v>
+        <v>5.8794</v>
       </c>
       <c r="C22" t="n">
-        <v>5.9348</v>
+        <v>5.9956</v>
       </c>
       <c r="D22" t="n">
-        <v>5.9757</v>
+        <v>6.0401</v>
       </c>
       <c r="E22" t="n">
-        <v>6.0679</v>
+        <v>6.1013</v>
       </c>
       <c r="F22" t="n">
-        <v>6.1473</v>
+        <v>6.1381</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2521</v>
+        <v>6.2096</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6961</v>
+        <v>6.695</v>
       </c>
       <c r="I22" t="n">
-        <v>7.0282</v>
+        <v>7.0277</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3671</v>
+        <v>7.367</v>
       </c>
       <c r="K22" t="n">
-        <v>7.686</v>
+        <v>7.6862</v>
       </c>
       <c r="L22" t="n">
-        <v>7.9605</v>
+        <v>7.961</v>
       </c>
       <c r="M22" t="n">
-        <v>8.166499999999999</v>
+        <v>8.1669</v>
       </c>
       <c r="N22" t="n">
-        <v>8.2758</v>
+        <v>8.2759</v>
       </c>
       <c r="O22" t="n">
-        <v>8.256600000000001</v>
+        <v>8.2561</v>
       </c>
       <c r="P22" t="n">
-        <v>8.076000000000001</v>
+        <v>8.074400000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
